--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3E5E15-548B-4991-8081-F53D9CA0428D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DB43EA-B52E-4722-A513-B23EB5219A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2364,9 +2364,6 @@
     <t>Sólo números enteros</t>
   </si>
   <si>
-    <t>No puede ser mayor a 24</t>
-  </si>
-  <si>
     <t>normas</t>
   </si>
   <si>
@@ -3091,6 +3088,9 @@
   </si>
   <si>
     <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que los datos que se ingresaron no pertenecen a ningun inmueble.</t>
+  </si>
+  <si>
+    <t>no puede ser negativo</t>
   </si>
 </sst>
 </file>
@@ -3814,7 +3814,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4012,6 +4012,33 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4033,6 +4060,63 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4114,63 +4198,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4180,6 +4207,36 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4216,35 +4273,74 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4255,120 +4351,39 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4381,21 +4396,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4408,7 +4408,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4419,12 +4419,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4841,10 +4835,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="79"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4954,11 +4948,11 @@
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="72"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -4984,7 +4978,7 @@
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="73" t="str">
+      <c r="D3" s="82" t="str">
         <f>$B$1</f>
         <v>Residentes</v>
       </c>
@@ -4999,7 +4993,7 @@
       <c r="C4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -5011,7 +5005,7 @@
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="74"/>
+      <c r="D5" s="83"/>
     </row>
     <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -5023,7 +5017,7 @@
       <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
@@ -5035,7 +5029,7 @@
       <c r="C7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="75"/>
+      <c r="D7" s="84"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="18"/>
@@ -5090,73 +5084,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="89" t="str">
         <f>'Listado Objetos Dominio'!A3</f>
         <v>ConjuntoResidencial</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="90" t="str">
         <f>'Listado Objetos Dominio'!B3</f>
         <v>Objeto de dominio que representa cada una de las comunidades habitacionales organizadas en un sistema. Abarca la totalidad de los elementos que componen el conjunto, desde las unidades habitacionales individuales (inmuebles) hasta las zonas comunes.</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
@@ -5265,19 +5259,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
@@ -5320,27 +5314,27 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="25">
         <v>14</v>
@@ -5353,7 +5347,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="27" t="s">
@@ -5375,27 +5369,27 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R7" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S7" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="25">
         <v>1</v>
@@ -5408,7 +5402,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J8" s="25"/>
       <c r="K8" s="27" t="s">
@@ -5430,27 +5424,27 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R8" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S8" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S8" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T8" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="25">
         <v>1</v>
@@ -5463,7 +5457,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
@@ -5485,24 +5479,24 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R9" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S9" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T9" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U9" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>13</v>
@@ -5518,11 +5512,11 @@
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J10" s="25"/>
       <c r="K10" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L10" s="28" t="s">
         <v>52</v>
@@ -5540,19 +5534,19 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
@@ -5595,27 +5589,27 @@
         <v>52</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R11" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U11" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -5643,128 +5637,128 @@
       </c>
       <c r="Q12" s="26"/>
       <c r="R12" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U12" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
+      <c r="E14" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="E14" s="115" t="s">
-        <v>135</v>
-      </c>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="34" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="92" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="116" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="117" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="116" t="s">
+      <c r="F16" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="116" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="118" t="s">
-        <v>121</v>
+      <c r="G16" s="94" t="s">
+        <v>120</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="116"/>
-      <c r="B17" s="116"/>
-      <c r="C17" s="117"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="119"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="95"/>
     </row>
     <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="120" t="s">
+      <c r="A19" s="96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103" t="s">
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103" t="s">
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="L19" s="103"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="103" t="s">
+      <c r="Q19" s="85"/>
+      <c r="R19" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103" t="s">
+      <c r="S19" s="86"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="97"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="S19" s="110"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="121"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="38" t="s">
+      <c r="I20" s="38" t="s">
         <v>71</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>72</v>
       </c>
       <c r="J20" s="38" t="s">
         <v>3</v>
@@ -5772,266 +5766,287 @@
       <c r="K20" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="111" t="s">
+      <c r="L20" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="111"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
+      <c r="M20" s="87"/>
+      <c r="N20" s="87"/>
+      <c r="O20" s="87"/>
       <c r="P20" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="38" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S20" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="S20" s="39" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="21" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="105"/>
+      <c r="C21" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S21" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="106"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="106"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="108"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="125" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="86" t="s">
+      <c r="B25" s="126"/>
+      <c r="C25" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="73" t="s">
-        <v>163</v>
-      </c>
-      <c r="I21" s="107" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="104" t="s">
-        <v>164</v>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="87"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="S21" s="60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="S22" s="60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="S24" s="60" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
       <c r="H25" s="42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I25" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="K25" s="43" t="s">
+      <c r="L25" s="127" t="s">
         <v>177</v>
       </c>
-      <c r="L25" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
       <c r="P25" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q25" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R25" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="S25" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="S25" s="63" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="26" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="102" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
+      <c r="A26" s="128" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="129"/>
+      <c r="C26" s="130" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="130"/>
       <c r="H26" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I26" s="47" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K26" s="48"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="95" t="s">
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="123" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q26" s="110" t="s">
         <v>194</v>
       </c>
-      <c r="Q26" s="82" t="s">
+      <c r="R26" s="110" t="s">
         <v>195</v>
       </c>
-      <c r="R26" s="82" t="s">
+      <c r="S26" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="S26" s="84" t="s">
-        <v>197</v>
-      </c>
     </row>
     <row r="27" spans="1:19" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="122" t="s">
-        <v>227</v>
-      </c>
-      <c r="B27" s="123"/>
-      <c r="C27" s="124" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
+      <c r="A27" s="131" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="132"/>
+      <c r="C27" s="133" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="133"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
       <c r="H27" s="59" t="s">
         <v>49</v>
       </c>
       <c r="I27" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="J27" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="50" t="s">
-        <v>182</v>
-      </c>
       <c r="K27" s="51"/>
-      <c r="L27" s="124"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="124"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="96"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="85"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="124"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="111"/>
+      <c r="S27" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A21:B24"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="S26:S27"/>
+    <mergeCell ref="L21:O24"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="C21:G24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="K19:O19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="H21:H24"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="A1:Q1"/>
@@ -6048,27 +6063,6 @@
     <mergeCell ref="A19:B20"/>
     <mergeCell ref="C19:G20"/>
     <mergeCell ref="H19:J19"/>
-    <mergeCell ref="K19:O19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="A21:B24"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="S26:S27"/>
-    <mergeCell ref="L21:O24"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="C21:G24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="L27:O27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{193F65CD-468D-4EE9-B635-8067A5B8EAA9}"/>
@@ -6123,73 +6117,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="89" t="str">
         <f>'Listado Objetos Dominio'!A4</f>
         <v>ZonaComun</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="90" t="str">
         <f>'Listado Objetos Dominio'!B4</f>
         <v>Objeto de dominio que representa a cada una de las zonas comunes que se encuentran dentro de un conjunto residencial para que los residentes puedan reservar esos espacios y poder usarlos.</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
@@ -6298,19 +6292,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
@@ -6353,19 +6347,19 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
@@ -6408,27 +6402,27 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R7" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S7" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -6457,40 +6451,44 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="G9" s="25">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>3600</v>
+      </c>
       <c r="I9" s="26" t="s">
         <v>57</v>
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>58</v>
+        <v>300</v>
       </c>
       <c r="L9" s="25" t="s">
         <v>52</v>
@@ -6508,24 +6506,24 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R9" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S9" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T9" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U9" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>8</v>
@@ -6557,24 +6555,24 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>8</v>
@@ -6612,27 +6610,27 @@
         <v>52</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R11" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U11" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -6659,105 +6657,105 @@
         <v>52</v>
       </c>
       <c r="Q12" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R12" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U12" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="140" t="s">
-        <v>134</v>
-      </c>
-      <c r="B14" s="141"/>
-      <c r="C14" s="142"/>
+      <c r="A14" s="134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="135"/>
+      <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="137" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="139" t="s">
         <v>155</v>
-      </c>
-      <c r="B16" s="145" t="s">
-        <v>156</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="144"/>
-      <c r="B17" s="146"/>
+      <c r="A17" s="138"/>
+      <c r="B17" s="140"/>
       <c r="C17" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="120" t="s">
+      <c r="A19" s="96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103" t="s">
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103" t="s">
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="L19" s="103"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="103" t="s">
+      <c r="Q19" s="85"/>
+      <c r="R19" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103" t="s">
+      <c r="S19" s="86"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="97"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="S19" s="110"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="121"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="38" t="s">
+      <c r="I20" s="38" t="s">
         <v>71</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>72</v>
       </c>
       <c r="J20" s="38" t="s">
         <v>3</v>
@@ -6765,245 +6763,245 @@
       <c r="K20" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="111" t="s">
+      <c r="L20" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="111"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
+      <c r="M20" s="87"/>
+      <c r="N20" s="87"/>
+      <c r="O20" s="87"/>
       <c r="P20" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="38" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S20" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="S20" s="39" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="21" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="105"/>
+      <c r="C21" s="114" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="I21" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="98" t="s">
+        <v>207</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S21" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="106"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="106"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="108"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="141" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="86" t="s">
+      <c r="B25" s="142"/>
+      <c r="C25" s="143" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="42" t="s">
         <v>206</v>
-      </c>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="I21" s="107" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="104" t="s">
-        <v>208</v>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="87"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="S21" s="60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="S22" s="60" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="S24" s="60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" s="138"/>
-      <c r="C25" s="139" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="42" t="s">
-        <v>207</v>
       </c>
       <c r="I25" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="K25" s="58" t="s">
         <v>219</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="L25" s="127" t="s">
         <v>220</v>
       </c>
-      <c r="L25" s="99" t="s">
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="29" t="s">
+      <c r="Q25" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R25" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="S25" s="63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="144" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="145"/>
+      <c r="C26" s="146" t="s">
         <v>222</v>
       </c>
-      <c r="Q25" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="R25" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="S25" s="63" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="125" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="127" t="s">
-        <v>223</v>
-      </c>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="127"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="146"/>
       <c r="H26" s="46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I26" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K26" s="48"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="130"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="148"/>
+      <c r="N26" s="148"/>
+      <c r="O26" s="149"/>
       <c r="P26" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q26" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="R26" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="R26" s="49" t="s">
+      <c r="S26" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>197</v>
-      </c>
     </row>
     <row r="27" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="131" t="s">
-        <v>227</v>
-      </c>
-      <c r="B27" s="132"/>
-      <c r="C27" s="133" t="s">
-        <v>224</v>
-      </c>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
+      <c r="A27" s="150" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="151"/>
+      <c r="C27" s="152" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
       <c r="H27" s="59" t="s">
         <v>49</v>
       </c>
@@ -7011,28 +7009,43 @@
         <v>9</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K27" s="51"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="194" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q27" s="195" t="s">
+      <c r="L27" s="153"/>
+      <c r="M27" s="154"/>
+      <c r="N27" s="154"/>
+      <c r="O27" s="155"/>
+      <c r="P27" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q27" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="R27" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="R27" s="195" t="s">
+      <c r="S27" s="75" t="s">
         <v>196</v>
-      </c>
-      <c r="S27" s="196" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="L21:O24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="C21:G24"/>
+    <mergeCell ref="A21:B24"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="A1:Q1"/>
@@ -7046,21 +7059,6 @@
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K19:O19"/>
     <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="L21:O24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="C21:G24"/>
-    <mergeCell ref="A21:B24"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="L27:O27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B8AB2723-0DBB-4F87-B341-FF92A393E7BB}"/>
@@ -7117,73 +7115,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="89" t="str">
         <f>'Listado Objetos Dominio'!A5</f>
         <v>Administrador</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="90" t="str">
         <f>'Listado Objetos Dominio'!B5</f>
         <v>Objeto de dominio que representa el Administrador encargado de hacer la creación o gestión de las zonas comunes y la gestión de residentes y sus respectivas reservas en caso de ser necesario.</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="55" t="s">
@@ -7292,19 +7290,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
@@ -7347,27 +7345,27 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="25">
         <v>1</v>
@@ -7402,24 +7400,24 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>8</v>
@@ -7457,24 +7455,24 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S8" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U8" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T8" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U8" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>13</v>
@@ -7490,11 +7488,11 @@
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>52</v>
@@ -7512,24 +7510,24 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R9" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S9" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T9" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U9" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T9" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U9" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>13</v>
@@ -7545,7 +7543,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J10" s="25"/>
       <c r="K10" s="27" t="s">
@@ -7567,27 +7565,27 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="25">
         <v>11</v>
@@ -7600,7 +7598,7 @@
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" s="25"/>
       <c r="K11" s="27"/>
@@ -7620,27 +7618,27 @@
         <v>52</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R11" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>189</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="U11" s="31" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="25">
         <v>8</v>
@@ -7653,7 +7651,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" s="25"/>
       <c r="K12" s="27"/>
@@ -7673,167 +7671,167 @@
         <v>52</v>
       </c>
       <c r="Q12" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R12" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U12" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="115" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="E15" s="115" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="I15" s="115" t="s">
-        <v>120</v>
-      </c>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
+      <c r="A15" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
+      <c r="E15" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="I15" s="91" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="91"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="34" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="34" t="s">
         <v>3</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="116" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="116" t="s">
+      <c r="A17" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="B17" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="93" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="93" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="92" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="92" t="s">
+        <v>115</v>
+      </c>
+      <c r="K17" s="93" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="92"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="93"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="93"/>
+    </row>
+    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="92"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="116" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="116" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="116" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="116" t="s">
-        <v>116</v>
-      </c>
-      <c r="K17" s="117" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="117"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="117"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="117"/>
-    </row>
-    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="117"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="117"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="93"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="93"/>
     </row>
     <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="120" t="s">
+      <c r="A21" s="96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103" t="s">
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103" t="s">
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="L21" s="103"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="103"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="103" t="s">
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="103" t="s">
+      <c r="S21" s="86"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="97"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="S21" s="110"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="121"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="38" t="s">
+      <c r="I22" s="38" t="s">
         <v>71</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>72</v>
       </c>
       <c r="J22" s="38" t="s">
         <v>3</v>
@@ -7841,195 +7839,195 @@
       <c r="K22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="111" t="s">
+      <c r="L22" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="87"/>
       <c r="P22" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="38" t="s">
         <v>3</v>
       </c>
       <c r="R22" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S22" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="S22" s="39" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="86" t="s">
-        <v>248</v>
-      </c>
-      <c r="D23" s="87"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="73" t="str">
+      <c r="A23" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="105"/>
+      <c r="C23" s="114" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="82" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
       </c>
-      <c r="I23" s="107" t="str">
+      <c r="I23" s="101" t="str">
         <f>B2</f>
         <v>Administrador</v>
       </c>
-      <c r="J23" s="104" t="str">
+      <c r="J23" s="98" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Administrador</v>
       </c>
       <c r="K23" s="16"/>
-      <c r="L23" s="86"/>
-      <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="88"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="116"/>
       <c r="P23" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="106"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="117"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="Q23" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="R23" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="78"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="14" t="s">
+      <c r="R24" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="106"/>
+      <c r="B25" s="107"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="118"/>
+      <c r="N25" s="118"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="Q24" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="R24" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="S24" s="60" t="s">
+      <c r="R25" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="S25" s="60" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="78"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="14" t="s">
+    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="106"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="Q25" s="13" t="s">
+      <c r="Q26" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="S26" s="60" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="108"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="121"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q27" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="R27" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="S25" s="60" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="108"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="S26" s="60" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="80"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="R27" s="13" t="s">
+      <c r="S27" s="60" t="s">
         <v>243</v>
       </c>
-      <c r="S27" s="60" t="s">
+    </row>
+    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="141" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="142"/>
+      <c r="C28" s="143" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="139" t="s">
-        <v>245</v>
-      </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="143"/>
+      <c r="G28" s="143"/>
       <c r="H28" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -8043,39 +8041,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de Administrador de un conjunto residencial.</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>220</v>
-      </c>
-      <c r="L28" s="99" t="s">
-        <v>251</v>
-      </c>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
+        <v>219</v>
+      </c>
+      <c r="L28" s="127" t="s">
+        <v>250</v>
+      </c>
+      <c r="M28" s="127"/>
+      <c r="N28" s="127"/>
+      <c r="O28" s="127"/>
       <c r="P28" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q28" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R28" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="S28" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="S28" s="63" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="29" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="125" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" s="126"/>
-      <c r="C29" s="127" t="s">
-        <v>249</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
+      <c r="A29" s="144" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="145"/>
+      <c r="C29" s="146" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="146"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="146"/>
       <c r="H29" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -8089,35 +8087,35 @@
         <v>Corresponde a los datos que se van a modificar de la Administrador</v>
       </c>
       <c r="K29" s="48"/>
-      <c r="L29" s="128"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="129"/>
-      <c r="O29" s="130"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="148"/>
+      <c r="N29" s="148"/>
+      <c r="O29" s="149"/>
       <c r="P29" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q29" s="49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R29" s="49" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S29" s="49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="131" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" s="132"/>
-      <c r="C30" s="133" t="s">
-        <v>250</v>
-      </c>
-      <c r="D30" s="133"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="133"/>
+      <c r="A30" s="150" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="151"/>
+      <c r="C30" s="152" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="152"/>
       <c r="H30" s="59" t="s">
         <v>49</v>
       </c>
@@ -8129,25 +8127,46 @@
         <v>Corresponde al identificador del Administrador  que se quiere dar de baja.</v>
       </c>
       <c r="K30" s="51"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="194" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q30" s="195" t="s">
-        <v>195</v>
-      </c>
-      <c r="R30" s="195" t="s">
-        <v>296</v>
-      </c>
-      <c r="S30" s="196" t="s">
-        <v>197</v>
+      <c r="L30" s="153"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="155"/>
+      <c r="P30" s="73" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q30" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="R30" s="74" t="s">
+        <v>295</v>
+      </c>
+      <c r="S30" s="75" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="L23:O27"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:O21"/>
+    <mergeCell ref="A23:B27"/>
+    <mergeCell ref="C23:G27"/>
+    <mergeCell ref="H23:H27"/>
+    <mergeCell ref="I23:I27"/>
+    <mergeCell ref="J23:J27"/>
     <mergeCell ref="G17:G19"/>
     <mergeCell ref="K17:K19"/>
     <mergeCell ref="R21:S21"/>
@@ -8164,27 +8183,6 @@
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="J17:J19"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="L23:O27"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K21:O21"/>
-    <mergeCell ref="A23:B27"/>
-    <mergeCell ref="C23:G27"/>
-    <mergeCell ref="H23:H27"/>
-    <mergeCell ref="I23:I27"/>
-    <mergeCell ref="J23:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B1A972F6-B36A-42D4-994E-AD97A6BC793F}"/>
@@ -8245,73 +8243,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="89" t="str">
         <f>'Listado Objetos Dominio'!A6</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="90" t="str">
         <f>'Listado Objetos Dominio'!B6</f>
         <v>Objeto de dominio que representa una zona de inmuebles en un conjunto residencial se refiere a una agrupación de unidades habitacionales (torre, bloque, lote) que comparten una ubicación fisica y caracteristicas comunes dentro del conjunto.</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
@@ -8366,7 +8364,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A22</f>
@@ -8419,24 +8417,24 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>8</v>
@@ -8452,7 +8450,7 @@
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
       <c r="I6" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J6" s="25"/>
       <c r="K6" s="27" t="s">
@@ -8474,24 +8472,24 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>13</v>
@@ -8507,11 +8505,11 @@
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>52</v>
@@ -8529,27 +8527,27 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -8576,113 +8574,112 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S8" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="140" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="141"/>
-      <c r="C10" s="142"/>
+      <c r="A10" s="134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="147" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="145" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="187" t="s">
-        <v>88</v>
+      <c r="A12" s="179" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="139" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="70" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="148"/>
-      <c r="B13" s="186"/>
+      <c r="A13" s="180"/>
+      <c r="B13" s="182"/>
       <c r="C13" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="185"/>
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:21" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="149"/>
-      <c r="B14" s="146"/>
+      <c r="A14" s="181"/>
+      <c r="B14" s="140"/>
       <c r="C14" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="177" t="s">
+      <c r="A16" s="183" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="184"/>
+      <c r="C16" s="187" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="188"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="188"/>
+      <c r="G16" s="184"/>
+      <c r="H16" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="173"/>
-      <c r="C16" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="172"/>
-      <c r="E16" s="172"/>
-      <c r="F16" s="172"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="168" t="s">
+      <c r="I16" s="191"/>
+      <c r="J16" s="192"/>
+      <c r="K16" s="174" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="170"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="168" t="s">
+      <c r="L16" s="191"/>
+      <c r="M16" s="191"/>
+      <c r="N16" s="191"/>
+      <c r="O16" s="192"/>
+      <c r="P16" s="174" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="170"/>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="168" t="s">
+      <c r="Q16" s="192"/>
+      <c r="R16" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="Q16" s="169"/>
-      <c r="R16" s="168" t="s">
+      <c r="S16" s="175"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="185"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="189"/>
+      <c r="D17" s="190"/>
+      <c r="E17" s="190"/>
+      <c r="F17" s="190"/>
+      <c r="G17" s="186"/>
+      <c r="H17" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="S16" s="182"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="178"/>
-      <c r="B17" s="176"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="175"/>
-      <c r="F17" s="175"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="38" t="s">
+      <c r="I17" s="38" t="s">
         <v>71</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>72</v>
       </c>
       <c r="J17" s="38" t="s">
         <v>3</v>
@@ -8690,38 +8687,38 @@
       <c r="K17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="179" t="s">
+      <c r="L17" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="180"/>
-      <c r="N17" s="180"/>
-      <c r="O17" s="181"/>
+      <c r="M17" s="177"/>
+      <c r="N17" s="177"/>
+      <c r="O17" s="178"/>
       <c r="P17" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="38" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S17" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="S17" s="39" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="18" spans="1:19" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="188" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="189"/>
+      <c r="A18" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="194"/>
       <c r="C18" s="197" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D18" s="198"/>
       <c r="E18" s="198"/>
       <c r="F18" s="198"/>
       <c r="G18" s="199"/>
-      <c r="H18" s="73" t="str">
+      <c r="H18" s="82" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
       </c>
@@ -8729,122 +8726,122 @@
         <f>B2</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="J18" s="104" t="str">
+      <c r="J18" s="98" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ZonaInmueble</v>
       </c>
       <c r="K18" s="16"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="87"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="88"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="116"/>
       <c r="P18" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q18" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="Q18" s="13" t="s">
-        <v>259</v>
-      </c>
       <c r="R18" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S18" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="S18" s="60" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="19" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="190"/>
-      <c r="B19" s="191"/>
+      <c r="A19" s="195"/>
+      <c r="B19" s="196"/>
       <c r="C19" s="200"/>
       <c r="D19" s="201"/>
       <c r="E19" s="201"/>
       <c r="F19" s="201"/>
       <c r="G19" s="202"/>
-      <c r="H19" s="74"/>
+      <c r="H19" s="83"/>
       <c r="I19" s="204"/>
-      <c r="J19" s="105"/>
+      <c r="J19" s="99"/>
       <c r="K19" s="61"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="183"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="91"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="119"/>
       <c r="P19" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q19" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="R19" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="R19" s="13" t="s">
+      <c r="S19" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="S19" s="60" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="190"/>
-      <c r="B20" s="191"/>
+      <c r="A20" s="195"/>
+      <c r="B20" s="196"/>
       <c r="C20" s="200"/>
       <c r="D20" s="201"/>
       <c r="E20" s="201"/>
       <c r="F20" s="201"/>
       <c r="G20" s="202"/>
-      <c r="H20" s="74"/>
+      <c r="H20" s="83"/>
       <c r="I20" s="204"/>
-      <c r="J20" s="105"/>
+      <c r="J20" s="99"/>
       <c r="K20" s="61"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="183"/>
-      <c r="N20" s="183"/>
-      <c r="O20" s="91"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R20" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="S20" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="S20" s="60" t="s">
-        <v>267</v>
-      </c>
     </row>
     <row r="21" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="190"/>
-      <c r="B21" s="191"/>
+      <c r="A21" s="195"/>
+      <c r="B21" s="196"/>
       <c r="C21" s="200"/>
       <c r="D21" s="201"/>
       <c r="E21" s="201"/>
       <c r="F21" s="201"/>
       <c r="G21" s="202"/>
-      <c r="H21" s="74"/>
+      <c r="H21" s="83"/>
       <c r="I21" s="204"/>
-      <c r="J21" s="105"/>
+      <c r="J21" s="99"/>
       <c r="K21" s="61"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="183"/>
-      <c r="N21" s="183"/>
-      <c r="O21" s="91"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="119"/>
       <c r="P21" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R21" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S21" s="60" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="166" t="s">
-        <v>158</v>
-      </c>
-      <c r="B22" s="167"/>
+      <c r="A22" s="161" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="162"/>
       <c r="C22" s="163" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D22" s="164"/>
       <c r="E22" s="164"/>
@@ -8863,39 +8860,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de ZonaInmueble de un conjunto residencial.</v>
       </c>
       <c r="K22" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="L22" s="166" t="s">
         <v>220</v>
       </c>
-      <c r="L22" s="160" t="s">
-        <v>221</v>
-      </c>
-      <c r="M22" s="161"/>
-      <c r="N22" s="161"/>
-      <c r="O22" s="162"/>
+      <c r="M22" s="167"/>
+      <c r="N22" s="167"/>
+      <c r="O22" s="168"/>
       <c r="P22" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q22" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R22" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="S22" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="S22" s="63" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="158" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="159"/>
-      <c r="C23" s="155" t="s">
-        <v>254</v>
-      </c>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="157"/>
+      <c r="A23" s="169" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="170"/>
+      <c r="C23" s="171" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="172"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="173"/>
       <c r="H23" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
@@ -8909,35 +8906,35 @@
         <v>Corresponde a los datos que se van a modificar de la ZonaInmueble</v>
       </c>
       <c r="K23" s="48"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="184" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q23" s="192" t="s">
-        <v>195</v>
-      </c>
-      <c r="R23" s="192" t="s">
-        <v>295</v>
-      </c>
-      <c r="S23" s="193" t="s">
-        <v>197</v>
+      <c r="L23" s="147"/>
+      <c r="M23" s="148"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="149"/>
+      <c r="P23" s="69" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q23" s="71" t="s">
+        <v>194</v>
+      </c>
+      <c r="R23" s="71" t="s">
+        <v>294</v>
+      </c>
+      <c r="S23" s="72" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="153" t="s">
-        <v>227</v>
-      </c>
-      <c r="B24" s="154"/>
-      <c r="C24" s="150" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="A24" s="156" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" s="157"/>
+      <c r="C24" s="158" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="160"/>
       <c r="H24" s="59" t="s">
         <v>49</v>
       </c>
@@ -8949,34 +8946,31 @@
         <v>Corresponde al identificador de la ZonaInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K24" s="51"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="135"/>
-      <c r="N24" s="135"/>
-      <c r="O24" s="136"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="154"/>
+      <c r="N24" s="154"/>
+      <c r="O24" s="155"/>
       <c r="P24" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S24" s="52" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="L18:O21"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="C18:G21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="A1:Q1"/>
@@ -8990,12 +8984,15 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="K16:O16"/>
     <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C18:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="J18:J21"/>
-    <mergeCell ref="L18:O21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{00F0F8F7-DC0F-4454-B174-288E79B7BE78}"/>
@@ -9034,7 +9031,7 @@
     <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.21875" style="205" customWidth="1"/>
+    <col min="8" max="8" width="35.21875" style="76" customWidth="1"/>
     <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
     <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
@@ -9053,73 +9050,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="89" t="str">
         <f>'Listado Objetos Dominio'!A7</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="90" t="str">
         <f>'Listado Objetos Dominio'!B7</f>
         <v>Objeto de dominio que representa un imnueble dentro de una zona de inmuebles en un conjunto residencial describe las caracteristicas especificasde una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona inmueble.</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
@@ -9174,7 +9171,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A23</f>
@@ -9227,24 +9224,24 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>8</v>
@@ -9260,7 +9257,7 @@
       <c r="G6" s="25"/>
       <c r="H6" s="26"/>
       <c r="I6" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J6" s="25"/>
       <c r="K6" s="27"/>
@@ -9280,27 +9277,27 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>95</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>96</v>
       </c>
       <c r="C7" s="25">
         <v>1</v>
@@ -9331,19 +9328,19 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -9368,116 +9365,116 @@
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S8" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="115"/>
-      <c r="C10" s="115"/>
+      <c r="A10" s="91" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="116" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="116" t="s">
+      <c r="A12" s="92" t="s">
         <v>143</v>
       </c>
-      <c r="C12" s="117" t="s">
-        <v>93</v>
+      <c r="B12" s="92" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="93" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
     </row>
     <row r="14" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="116"/>
-      <c r="B14" s="116"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="116"/>
-      <c r="B15" s="116"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="57" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="177" t="s">
+      <c r="A17" s="183" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="184"/>
+      <c r="C17" s="187" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="188"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="184"/>
+      <c r="H17" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="172"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="172"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="168" t="s">
+      <c r="I17" s="191"/>
+      <c r="J17" s="192"/>
+      <c r="K17" s="174" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="170"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="168" t="s">
+      <c r="L17" s="191"/>
+      <c r="M17" s="191"/>
+      <c r="N17" s="191"/>
+      <c r="O17" s="192"/>
+      <c r="P17" s="174" t="s">
         <v>68</v>
       </c>
-      <c r="L17" s="170"/>
-      <c r="M17" s="170"/>
-      <c r="N17" s="170"/>
-      <c r="O17" s="169"/>
-      <c r="P17" s="168" t="s">
+      <c r="Q17" s="192"/>
+      <c r="R17" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="Q17" s="169"/>
-      <c r="R17" s="168" t="s">
+      <c r="S17" s="175"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="185"/>
+      <c r="B18" s="186"/>
+      <c r="C18" s="189"/>
+      <c r="D18" s="190"/>
+      <c r="E18" s="190"/>
+      <c r="F18" s="190"/>
+      <c r="G18" s="186"/>
+      <c r="H18" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="S17" s="182"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="178"/>
-      <c r="B18" s="176"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="206" t="s">
+      <c r="I18" s="38" t="s">
         <v>71</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>72</v>
       </c>
       <c r="J18" s="38" t="s">
         <v>3</v>
@@ -9485,38 +9482,38 @@
       <c r="K18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="179" t="s">
+      <c r="L18" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="180"/>
-      <c r="N18" s="180"/>
-      <c r="O18" s="181"/>
+      <c r="M18" s="177"/>
+      <c r="N18" s="177"/>
+      <c r="O18" s="178"/>
       <c r="P18" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="38" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S18" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="S18" s="39" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="19" spans="1:19" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="188" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="189"/>
+      <c r="A19" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="194"/>
       <c r="C19" s="197" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D19" s="198"/>
       <c r="E19" s="198"/>
       <c r="F19" s="198"/>
       <c r="G19" s="199"/>
-      <c r="H19" s="207" t="str">
+      <c r="H19" s="205" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
@@ -9524,122 +9521,122 @@
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J19" s="104" t="str">
+      <c r="J19" s="98" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K19" s="16"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="88"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="115"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="116"/>
       <c r="P19" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R19" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="S19" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="S19" s="60" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="190"/>
-      <c r="B20" s="191"/>
+      <c r="A20" s="195"/>
+      <c r="B20" s="196"/>
       <c r="C20" s="200"/>
       <c r="D20" s="201"/>
       <c r="E20" s="201"/>
       <c r="F20" s="201"/>
       <c r="G20" s="202"/>
-      <c r="H20" s="208"/>
+      <c r="H20" s="206"/>
       <c r="I20" s="204"/>
-      <c r="J20" s="105"/>
+      <c r="J20" s="99"/>
       <c r="K20" s="61"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="183"/>
-      <c r="N20" s="183"/>
-      <c r="O20" s="91"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R20" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="S20" s="60" t="s">
         <v>286</v>
       </c>
-      <c r="S20" s="60" t="s">
-        <v>287</v>
-      </c>
     </row>
     <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="190"/>
-      <c r="B21" s="191"/>
+      <c r="A21" s="195"/>
+      <c r="B21" s="196"/>
       <c r="C21" s="200"/>
       <c r="D21" s="201"/>
       <c r="E21" s="201"/>
       <c r="F21" s="201"/>
       <c r="G21" s="202"/>
-      <c r="H21" s="208"/>
+      <c r="H21" s="206"/>
       <c r="I21" s="204"/>
-      <c r="J21" s="105"/>
+      <c r="J21" s="99"/>
       <c r="K21" s="61"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="183"/>
-      <c r="N21" s="183"/>
-      <c r="O21" s="91"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="119"/>
       <c r="P21" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R21" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="S21" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="S21" s="60" t="s">
-        <v>289</v>
-      </c>
     </row>
     <row r="22" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="190"/>
-      <c r="B22" s="191"/>
+      <c r="A22" s="195"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="200"/>
       <c r="D22" s="201"/>
       <c r="E22" s="201"/>
       <c r="F22" s="201"/>
       <c r="G22" s="202"/>
-      <c r="H22" s="208"/>
+      <c r="H22" s="206"/>
       <c r="I22" s="204"/>
-      <c r="J22" s="105"/>
+      <c r="J22" s="99"/>
       <c r="K22" s="61"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="183"/>
-      <c r="N22" s="183"/>
-      <c r="O22" s="91"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="119"/>
       <c r="P22" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R22" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="S22" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="S22" s="60" t="s">
-        <v>291</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="166" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="167"/>
+      <c r="A23" s="161" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="162"/>
       <c r="C23" s="163" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D23" s="164"/>
       <c r="E23" s="164"/>
@@ -9658,39 +9655,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de Inmueble de un conjunto residencial.</v>
       </c>
       <c r="K23" s="58" t="s">
-        <v>220</v>
-      </c>
-      <c r="L23" s="160" t="s">
-        <v>275</v>
-      </c>
-      <c r="M23" s="161"/>
-      <c r="N23" s="161"/>
-      <c r="O23" s="162"/>
+        <v>219</v>
+      </c>
+      <c r="L23" s="166" t="s">
+        <v>274</v>
+      </c>
+      <c r="M23" s="167"/>
+      <c r="N23" s="167"/>
+      <c r="O23" s="168"/>
       <c r="P23" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q23" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R23" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="S23" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="S23" s="63" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="158" t="s">
-        <v>159</v>
-      </c>
-      <c r="B24" s="159"/>
-      <c r="C24" s="155" t="s">
-        <v>273</v>
-      </c>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="157"/>
+      <c r="A24" s="169" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="170"/>
+      <c r="C24" s="171" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="172"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="173"/>
       <c r="H24" s="45" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -9704,35 +9701,35 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K24" s="48"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="129"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="184" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q24" s="192" t="s">
-        <v>195</v>
-      </c>
-      <c r="R24" s="192" t="s">
-        <v>300</v>
-      </c>
-      <c r="S24" s="193" t="s">
-        <v>197</v>
+      <c r="L24" s="147"/>
+      <c r="M24" s="148"/>
+      <c r="N24" s="148"/>
+      <c r="O24" s="149"/>
+      <c r="P24" s="69" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q24" s="71" t="s">
+        <v>194</v>
+      </c>
+      <c r="R24" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="S24" s="72" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="153" t="s">
-        <v>227</v>
-      </c>
-      <c r="B25" s="154"/>
-      <c r="C25" s="150" t="s">
-        <v>274</v>
-      </c>
-      <c r="D25" s="151"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="152"/>
+      <c r="A25" s="156" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="157"/>
+      <c r="C25" s="158" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="160"/>
       <c r="H25" s="50" t="s">
         <v>49</v>
       </c>
@@ -9744,34 +9741,31 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="51"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="135"/>
-      <c r="N25" s="135"/>
-      <c r="O25" s="136"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="154"/>
+      <c r="N25" s="154"/>
+      <c r="O25" s="155"/>
       <c r="P25" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S25" s="52" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L19:O22"/>
+    <mergeCell ref="A19:B22"/>
+    <mergeCell ref="C19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="A1:Q1"/>
@@ -9786,12 +9780,15 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="K17:O17"/>
     <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="C19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="L19:O22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{E9339FF0-C25B-4ACF-BE04-E905DF5A13F0}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84E10F9-8F2E-4087-8ACD-72C0EBE80AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73450C3-3A49-49B0-A7B5-446B11AA43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21240" yWindow="1695" windowWidth="16935" windowHeight="15345" firstSheet="4" activeTab="4" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
+    <workbookView xWindow="20805" yWindow="2265" windowWidth="18045" windowHeight="15345" firstSheet="7" activeTab="10" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3478,7 +3478,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="324">
   <si>
     <t>Referenciado</t>
   </si>
@@ -3736,9 +3736,6 @@
   </si>
   <si>
     <t>tipoZonaInmueble</t>
-  </si>
-  <si>
-    <t>Sólo letras</t>
   </si>
   <si>
     <t>numeroZonaInmueble</t>
@@ -5416,6 +5413,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5437,9 +5443,117 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5476,113 +5590,50 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5605,50 +5656,101 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5704,116 +5806,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6224,10 +6221,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="79"/>
+      <c r="B1" s="82"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -6342,73 +6339,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A7</f>
         <v>TipoInmueble</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B7</f>
         <v>Objeto de dominio que representa un tipo de inmueble encargado de hacer la creación de nuevos tipos inmuebles para el conjunto residencial como casas, apartamentos, glamplins  etc .</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -6463,7 +6460,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A19</f>
@@ -6516,19 +6513,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -6536,7 +6533,7 @@
         <v>53</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="C6" s="25">
         <v>1</v>
@@ -6569,27 +6566,27 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
@@ -6603,64 +6600,64 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="131" t="s">
+        <v>320</v>
+      </c>
+      <c r="B10" s="131" t="s">
         <v>321</v>
       </c>
-      <c r="B10" s="92" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="93" t="str">
+      <c r="C10" s="132" t="str">
         <f>A6</f>
         <v>nombre</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="92"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="132"/>
     </row>
     <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="183" t="s">
+      <c r="A13" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="184"/>
-      <c r="C13" s="187" t="s">
+      <c r="B13" s="182"/>
+      <c r="C13" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="188"/>
-      <c r="G13" s="184"/>
-      <c r="H13" s="174" t="s">
+      <c r="D13" s="186"/>
+      <c r="E13" s="186"/>
+      <c r="F13" s="186"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="191"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="174" t="s">
+      <c r="I13" s="189"/>
+      <c r="J13" s="190"/>
+      <c r="K13" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="191"/>
-      <c r="M13" s="191"/>
-      <c r="N13" s="191"/>
-      <c r="O13" s="192"/>
-      <c r="P13" s="174" t="s">
+      <c r="L13" s="189"/>
+      <c r="M13" s="189"/>
+      <c r="N13" s="189"/>
+      <c r="O13" s="190"/>
+      <c r="P13" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="Q13" s="192"/>
-      <c r="R13" s="174" t="s">
+      <c r="Q13" s="190"/>
+      <c r="R13" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="S13" s="175"/>
+      <c r="S13" s="173"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="185"/>
-      <c r="B14" s="186"/>
-      <c r="C14" s="189"/>
-      <c r="D14" s="190"/>
-      <c r="E14" s="190"/>
-      <c r="F14" s="190"/>
-      <c r="G14" s="186"/>
+      <c r="A14" s="183"/>
+      <c r="B14" s="184"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="188"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="188"/>
+      <c r="G14" s="184"/>
       <c r="H14" s="77" t="s">
         <v>70</v>
       </c>
@@ -6673,12 +6670,12 @@
       <c r="K14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="176" t="s">
+      <c r="L14" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="177"/>
-      <c r="N14" s="177"/>
-      <c r="O14" s="178"/>
+      <c r="M14" s="175"/>
+      <c r="N14" s="175"/>
+      <c r="O14" s="176"/>
       <c r="P14" s="38" t="s">
         <v>72</v>
       </c>
@@ -6693,146 +6690,146 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="193" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="194"/>
-      <c r="C15" s="197" t="s">
-        <v>266</v>
-      </c>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="198"/>
-      <c r="G15" s="199"/>
-      <c r="H15" s="205" t="str">
+      <c r="A15" s="160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="161"/>
+      <c r="C15" s="164" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="166"/>
+      <c r="H15" s="209" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
       </c>
-      <c r="I15" s="203" t="str">
+      <c r="I15" s="170" t="str">
         <f>B2</f>
         <v>TipoInmueble</v>
       </c>
-      <c r="J15" s="98" t="str">
+      <c r="J15" s="119" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva TipoInmueble</v>
       </c>
       <c r="K15" s="16"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="116"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="100"/>
       <c r="P15" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S15" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="210"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="102"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="Q15" s="13" t="s">
+      <c r="Q16" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S15" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="195"/>
-      <c r="B16" s="196"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="201"/>
-      <c r="G16" s="202"/>
-      <c r="H16" s="206"/>
-      <c r="I16" s="204"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="14" t="s">
+      <c r="R16" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="S16" s="60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="162"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="171"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="102"/>
+      <c r="N17" s="102"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="Q16" s="13" t="s">
+      <c r="Q17" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="R16" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="S16" s="60" t="s">
+      <c r="R17" s="13" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="195"/>
-      <c r="B17" s="196"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="206"/>
-      <c r="I17" s="204"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="118"/>
-      <c r="N17" s="118"/>
-      <c r="O17" s="119"/>
-      <c r="P17" s="14" t="s">
+      <c r="S17" s="60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="167"/>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="169"/>
+      <c r="H18" s="210"/>
+      <c r="I18" s="171"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="Q17" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="S17" s="60" t="s">
+      <c r="Q18" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="R18" s="13" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="195"/>
-      <c r="B18" s="196"/>
-      <c r="C18" s="200"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="201"/>
-      <c r="G18" s="202"/>
-      <c r="H18" s="206"/>
-      <c r="I18" s="204"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="119"/>
-      <c r="P18" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q18" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="R18" s="13" t="s">
+      <c r="S18" s="60" t="s">
         <v>285</v>
       </c>
-      <c r="S18" s="60" t="s">
-        <v>286</v>
-      </c>
     </row>
     <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="B19" s="162"/>
-      <c r="C19" s="163" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="A19" s="196" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="197"/>
+      <c r="C19" s="198" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="199"/>
+      <c r="E19" s="199"/>
+      <c r="F19" s="199"/>
+      <c r="G19" s="200"/>
       <c r="H19" s="41" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
@@ -6846,39 +6843,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de TipoInmueble de un conjunto residencial.</v>
       </c>
       <c r="K19" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="L19" s="166" t="s">
-        <v>270</v>
-      </c>
-      <c r="M19" s="167"/>
-      <c r="N19" s="167"/>
-      <c r="O19" s="168"/>
+        <v>214</v>
+      </c>
+      <c r="L19" s="201" t="s">
+        <v>269</v>
+      </c>
+      <c r="M19" s="202"/>
+      <c r="N19" s="202"/>
+      <c r="O19" s="203"/>
       <c r="P19" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q19" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R19" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S19" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S19" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="169" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="170"/>
-      <c r="C20" s="171" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="172"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="172"/>
-      <c r="G20" s="173"/>
+      <c r="A20" s="204" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="205"/>
+      <c r="C20" s="206" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="207"/>
+      <c r="E20" s="207"/>
+      <c r="F20" s="207"/>
+      <c r="G20" s="208"/>
       <c r="H20" s="45" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
@@ -6892,35 +6889,35 @@
         <v>Corresponde a los datos que se van a modificar de la TipoInmueble</v>
       </c>
       <c r="K20" s="48"/>
-      <c r="L20" s="147"/>
-      <c r="M20" s="148"/>
-      <c r="N20" s="148"/>
-      <c r="O20" s="149"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="142"/>
       <c r="P20" s="69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q20" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R20" s="71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S20" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="156" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="157"/>
-      <c r="C21" s="158" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="160"/>
+      <c r="A21" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="192"/>
+      <c r="C21" s="193" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="194"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="194"/>
+      <c r="G21" s="195"/>
       <c r="H21" s="50" t="s">
         <v>49</v>
       </c>
@@ -6932,44 +6929,25 @@
         <v>Corresponde al identificador de la TipoInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K21" s="51"/>
-      <c r="L21" s="153"/>
-      <c r="M21" s="154"/>
-      <c r="N21" s="154"/>
-      <c r="O21" s="155"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="147"/>
+      <c r="N21" s="147"/>
+      <c r="O21" s="148"/>
       <c r="P21" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R21" s="52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S21" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="A15:B18"/>
-    <mergeCell ref="C15:G18"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="L15:O18"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="C13:G14"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:O13"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="R13:S13"/>
     <mergeCell ref="L14:O14"/>
@@ -6980,6 +6958,25 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
+    <mergeCell ref="L15:O18"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:G14"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:O13"/>
+    <mergeCell ref="A15:B18"/>
+    <mergeCell ref="C15:G18"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="L20:O20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{D07C8615-2E2B-411D-8DD3-94AE21459CC4}"/>
@@ -7035,73 +7032,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A10</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B10</f>
         <v>Objeto de dominio que representa un imnueble dentro de una zona de inmuebles en un conjunto residencial describe las caracteristicas especificasde una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona inmueble.</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -7156,7 +7153,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A23</f>
@@ -7209,27 +7206,27 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="C6" s="25">
         <v>1</v>
@@ -7260,27 +7257,27 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
@@ -7297,19 +7294,19 @@
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
@@ -7334,27 +7331,27 @@
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S8" s="44" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
@@ -7368,77 +7365,77 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="92" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="92" t="s">
+      <c r="A12" s="131" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="B12" s="131" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="132" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="131"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="132"/>
+    </row>
+    <row r="14" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="131"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="57" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-    </row>
-    <row r="14" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="92"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="57" t="s">
-        <v>91</v>
-      </c>
-    </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="92"/>
-      <c r="B15" s="92"/>
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
       <c r="C15" s="57" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="183" t="s">
+      <c r="A17" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="184"/>
-      <c r="C17" s="187" t="s">
+      <c r="B17" s="182"/>
+      <c r="C17" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="188"/>
-      <c r="E17" s="188"/>
-      <c r="F17" s="188"/>
-      <c r="G17" s="184"/>
-      <c r="H17" s="174" t="s">
+      <c r="D17" s="186"/>
+      <c r="E17" s="186"/>
+      <c r="F17" s="186"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="191"/>
-      <c r="J17" s="192"/>
-      <c r="K17" s="174" t="s">
+      <c r="I17" s="189"/>
+      <c r="J17" s="190"/>
+      <c r="K17" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="191"/>
-      <c r="M17" s="191"/>
-      <c r="N17" s="191"/>
-      <c r="O17" s="192"/>
-      <c r="P17" s="174" t="s">
+      <c r="L17" s="189"/>
+      <c r="M17" s="189"/>
+      <c r="N17" s="189"/>
+      <c r="O17" s="190"/>
+      <c r="P17" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="Q17" s="192"/>
-      <c r="R17" s="174" t="s">
+      <c r="Q17" s="190"/>
+      <c r="R17" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="S17" s="175"/>
+      <c r="S17" s="173"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="185"/>
-      <c r="B18" s="186"/>
-      <c r="C18" s="189"/>
-      <c r="D18" s="190"/>
-      <c r="E18" s="190"/>
-      <c r="F18" s="190"/>
-      <c r="G18" s="186"/>
+      <c r="A18" s="183"/>
+      <c r="B18" s="184"/>
+      <c r="C18" s="187"/>
+      <c r="D18" s="188"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
+      <c r="G18" s="184"/>
       <c r="H18" s="77" t="s">
         <v>70</v>
       </c>
@@ -7451,12 +7448,12 @@
       <c r="K18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="176" t="s">
+      <c r="L18" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="177"/>
-      <c r="N18" s="177"/>
-      <c r="O18" s="178"/>
+      <c r="M18" s="175"/>
+      <c r="N18" s="175"/>
+      <c r="O18" s="176"/>
       <c r="P18" s="38" t="s">
         <v>72</v>
       </c>
@@ -7471,146 +7468,146 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="193" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="194"/>
-      <c r="C19" s="197" t="s">
-        <v>266</v>
-      </c>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="199"/>
-      <c r="H19" s="205" t="str">
+      <c r="A19" s="160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="161"/>
+      <c r="C19" s="164" t="s">
+        <v>265</v>
+      </c>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="209" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I19" s="203" t="str">
+      <c r="I19" s="170" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J19" s="98" t="str">
+      <c r="J19" s="119" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K19" s="16"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="116"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="100"/>
       <c r="P19" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S19" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="162"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="168"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="210"/>
+      <c r="I20" s="171"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
+      <c r="N20" s="102"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="Q19" s="13" t="s">
+      <c r="Q20" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="R19" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S19" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="195"/>
-      <c r="B20" s="196"/>
-      <c r="C20" s="200"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="201"/>
-      <c r="G20" s="202"/>
-      <c r="H20" s="206"/>
-      <c r="I20" s="204"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="14" t="s">
+      <c r="R20" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="S20" s="60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="162"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="168"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="210"/>
+      <c r="I21" s="171"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="102"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="Q20" s="13" t="s">
+      <c r="Q21" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="R20" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="S20" s="60" t="s">
+      <c r="R21" s="13" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="195"/>
-      <c r="B21" s="196"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="201"/>
-      <c r="F21" s="201"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="206"/>
-      <c r="I21" s="204"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="14" t="s">
+      <c r="S21" s="60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="162"/>
+      <c r="B22" s="163"/>
+      <c r="C22" s="167"/>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="169"/>
+      <c r="H22" s="210"/>
+      <c r="I22" s="171"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="Q21" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="S21" s="60" t="s">
+      <c r="Q22" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="R22" s="13" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="195"/>
-      <c r="B22" s="196"/>
-      <c r="C22" s="200"/>
-      <c r="D22" s="201"/>
-      <c r="E22" s="201"/>
-      <c r="F22" s="201"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="206"/>
-      <c r="I22" s="204"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="R22" s="13" t="s">
+      <c r="S22" s="60" t="s">
         <v>285</v>
       </c>
-      <c r="S22" s="60" t="s">
-        <v>286</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="B23" s="162"/>
-      <c r="C23" s="163" t="s">
-        <v>267</v>
-      </c>
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="165"/>
+      <c r="A23" s="196" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="197"/>
+      <c r="C23" s="198" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="199"/>
+      <c r="E23" s="199"/>
+      <c r="F23" s="199"/>
+      <c r="G23" s="200"/>
       <c r="H23" s="41" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -7624,39 +7621,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de Inmueble de un conjunto residencial.</v>
       </c>
       <c r="K23" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="L23" s="166" t="s">
-        <v>270</v>
-      </c>
-      <c r="M23" s="167"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="168"/>
+        <v>214</v>
+      </c>
+      <c r="L23" s="201" t="s">
+        <v>269</v>
+      </c>
+      <c r="M23" s="202"/>
+      <c r="N23" s="202"/>
+      <c r="O23" s="203"/>
       <c r="P23" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q23" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R23" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S23" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S23" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="169" t="s">
-        <v>154</v>
-      </c>
-      <c r="B24" s="170"/>
-      <c r="C24" s="171" t="s">
-        <v>268</v>
-      </c>
-      <c r="D24" s="172"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="173"/>
+      <c r="A24" s="204" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="205"/>
+      <c r="C24" s="206" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="207"/>
+      <c r="E24" s="207"/>
+      <c r="F24" s="207"/>
+      <c r="G24" s="208"/>
       <c r="H24" s="45" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -7670,35 +7667,35 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K24" s="48"/>
-      <c r="L24" s="147"/>
-      <c r="M24" s="148"/>
-      <c r="N24" s="148"/>
-      <c r="O24" s="149"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="141"/>
+      <c r="O24" s="142"/>
       <c r="P24" s="69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q24" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R24" s="71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S24" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="156" t="s">
-        <v>222</v>
-      </c>
-      <c r="B25" s="157"/>
-      <c r="C25" s="158" t="s">
-        <v>269</v>
-      </c>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="160"/>
+      <c r="A25" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" s="192"/>
+      <c r="C25" s="193" t="s">
+        <v>268</v>
+      </c>
+      <c r="D25" s="194"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="194"/>
+      <c r="G25" s="195"/>
       <c r="H25" s="50" t="s">
         <v>49</v>
       </c>
@@ -7710,31 +7707,34 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="51"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="154"/>
-      <c r="N25" s="154"/>
-      <c r="O25" s="155"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="147"/>
+      <c r="N25" s="147"/>
+      <c r="O25" s="148"/>
       <c r="P25" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S25" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="L19:O22"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="C19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="A1:Q1"/>
@@ -7749,15 +7749,12 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="K17:O17"/>
     <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L19:O22"/>
+    <mergeCell ref="A19:B22"/>
+    <mergeCell ref="C19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{E9339FF0-C25B-4ACF-BE04-E905DF5A13F0}"/>
@@ -7809,11 +7806,11 @@
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="81"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="84"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -7839,7 +7836,7 @@
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="82" t="str">
+      <c r="D3" s="85" t="str">
         <f>$B$1</f>
         <v>Residentes</v>
       </c>
@@ -7854,7 +7851,7 @@
       <c r="C4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="83"/>
+      <c r="D4" s="86"/>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -7866,7 +7863,7 @@
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="83"/>
+      <c r="D5" s="86"/>
     </row>
     <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
@@ -7878,43 +7875,43 @@
       <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="83"/>
+      <c r="D6" s="86"/>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="83"/>
+      <c r="D7" s="86"/>
     </row>
     <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="83"/>
+      <c r="D8" s="86"/>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="83"/>
+      <c r="D9" s="86"/>
     </row>
     <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
@@ -7926,7 +7923,7 @@
       <c r="C10" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="84"/>
+      <c r="D10" s="87"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
@@ -7984,73 +7981,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A3</f>
         <v>ConjuntoResidencial</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B3</f>
         <v>Objeto de dominio que representa cada una de las comunidades habitacionales organizadas en un sistema. Abarca la totalidad de los elementos que componen el conjunto, desde las unidades habitacionales individuales (inmuebles) hasta las zonas comunes.</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -8159,19 +8156,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -8214,24 +8211,24 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>8</v>
@@ -8269,19 +8266,19 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R7" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S7" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -8304,7 +8301,7 @@
       <c r="I8" s="26"/>
       <c r="J8" s="25"/>
       <c r="K8" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>52</v>
@@ -8322,24 +8319,24 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R8" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S8" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S8" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T8" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>13</v>
@@ -8359,7 +8356,7 @@
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>52</v>
@@ -8377,19 +8374,19 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R9" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S9" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T9" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U9" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T9" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U9" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -8430,19 +8427,19 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8461,7 +8458,7 @@
       <c r="I11" s="26"/>
       <c r="J11" s="25"/>
       <c r="K11" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L11" s="28" t="s">
         <v>52</v>
@@ -8480,29 +8477,29 @@
       </c>
       <c r="Q11" s="26"/>
       <c r="R11" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S11" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U11" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="91" t="s">
+      <c r="A13" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="E13" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="E13" s="91" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
@@ -8525,78 +8522,78 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="131" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="131" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="132" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="131" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="93" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="92" t="s">
+      <c r="F15" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="92" t="s">
-        <v>128</v>
-      </c>
-      <c r="G15" s="94" t="s">
-        <v>117</v>
+      <c r="G15" s="133" t="s">
+        <v>116</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="92"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="95"/>
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="132"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="134"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85" t="s">
+      <c r="B18" s="118"/>
+      <c r="C18" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85" t="s">
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="85"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85" t="s">
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85"/>
-      <c r="P18" s="85" t="s">
+      <c r="L18" s="118"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="Q18" s="85"/>
-      <c r="R18" s="85" t="s">
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="S18" s="86"/>
+      <c r="S18" s="125"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="97"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
+      <c r="A19" s="136"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
       <c r="H19" s="38" t="s">
         <v>70</v>
       </c>
@@ -8609,12 +8606,12 @@
       <c r="K19" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="87" t="s">
+      <c r="L19" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="87"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
       <c r="P19" s="38" t="s">
         <v>72</v>
       </c>
@@ -8629,246 +8626,267 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" s="89"/>
+      <c r="C20" s="98" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="122" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="119" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="99"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S20" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="90"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="102"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="S21" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="90"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="92"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="109" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="114" t="s">
+      <c r="B24" s="110"/>
+      <c r="C24" s="111" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="82" t="s">
-        <v>158</v>
-      </c>
-      <c r="I20" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="98" t="s">
-        <v>159</v>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S20" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="106"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="S21" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="106"/>
-      <c r="B22" s="107"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="S22" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
-      <c r="B23" s="109"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="122"/>
-      <c r="P23" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="125" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="127" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
       <c r="H24" s="42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I24" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="K24" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="K24" s="43" t="s">
+      <c r="L24" s="111" t="s">
         <v>172</v>
       </c>
-      <c r="L24" s="127" t="s">
-        <v>173</v>
-      </c>
-      <c r="M24" s="127"/>
-      <c r="N24" s="127"/>
-      <c r="O24" s="127"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
       <c r="P24" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q24" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R24" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S24" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S24" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="25" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="129"/>
-      <c r="C25" s="130" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="130"/>
+      <c r="A25" s="112" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="113"/>
+      <c r="C25" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
       <c r="H25" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I25" s="47" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K25" s="48"/>
-      <c r="L25" s="130"/>
-      <c r="M25" s="130"/>
-      <c r="N25" s="130"/>
-      <c r="O25" s="130"/>
-      <c r="P25" s="123" t="s">
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q25" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="Q25" s="110" t="s">
+      <c r="R25" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="R25" s="110" t="s">
+      <c r="S25" s="96" t="s">
         <v>191</v>
       </c>
-      <c r="S25" s="112" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="26" spans="1:19" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="131" t="s">
-        <v>222</v>
-      </c>
-      <c r="B26" s="132"/>
-      <c r="C26" s="133" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
+      <c r="A26" s="115" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="116"/>
+      <c r="C26" s="117" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
       <c r="H26" s="59" t="s">
         <v>49</v>
       </c>
       <c r="I26" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="J26" s="50" t="s">
-        <v>177</v>
-      </c>
       <c r="K26" s="51"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="133"/>
-      <c r="N26" s="133"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="124"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="113"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="117"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="108"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="J20:J23"/>
+    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="H20:H23"/>
     <mergeCell ref="A20:B23"/>
     <mergeCell ref="R25:R26"/>
     <mergeCell ref="S25:S26"/>
@@ -8885,27 +8903,6 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="L26:O26"/>
-    <mergeCell ref="K18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="J20:J23"/>
-    <mergeCell ref="I20:I23"/>
-    <mergeCell ref="H20:H23"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{193F65CD-468D-4EE9-B635-8067A5B8EAA9}"/>
@@ -8960,73 +8957,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A4</f>
         <v>ZonaComun</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B4</f>
         <v>Objeto de dominio que representa a cada una de las zonas comunes que se encuentran dentro de un conjunto residencial para que los residentes puedan reservar esos espacios y poder usarlos.</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -9135,19 +9132,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -9190,19 +9187,19 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -9245,27 +9242,27 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R7" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S7" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="25">
         <v>1</v>
@@ -9282,7 +9279,7 @@
       </c>
       <c r="J8" s="25"/>
       <c r="K8" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>52</v>
@@ -9300,27 +9297,27 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="25">
         <v>1</v>
@@ -9341,7 +9338,7 @@
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L9" s="25" t="s">
         <v>52</v>
@@ -9359,19 +9356,19 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R9" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T9" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U9" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -9414,27 +9411,27 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -9447,7 +9444,7 @@
       </c>
       <c r="J11" s="25"/>
       <c r="K11" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L11" s="25" t="s">
         <v>52</v>
@@ -9465,19 +9462,19 @@
         <v>52</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R11" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U11" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9496,7 +9493,7 @@
       <c r="I12" s="26"/>
       <c r="J12" s="25"/>
       <c r="K12" s="27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>51</v>
@@ -9517,25 +9514,25 @@
         <v>61</v>
       </c>
       <c r="R12" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U12" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="134" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="135"/>
-      <c r="C14" s="136"/>
+      <c r="A14" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="153"/>
+      <c r="C14" s="154"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
@@ -9549,65 +9546,65 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="137" t="s">
+      <c r="A16" s="155" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="157" t="s">
         <v>150</v>
-      </c>
-      <c r="B16" s="139" t="s">
-        <v>151</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="138"/>
-      <c r="B17" s="140"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="158"/>
       <c r="C17" s="37" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85" t="s">
+      <c r="B19" s="118"/>
+      <c r="C19" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85" t="s">
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="85"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="85" t="s">
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="85" t="s">
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="Q19" s="85"/>
-      <c r="R19" s="85" t="s">
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="S19" s="86"/>
+      <c r="S19" s="125"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="97"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
+      <c r="A20" s="136"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
       <c r="H20" s="38" t="s">
         <v>70</v>
       </c>
@@ -9620,12 +9617,12 @@
       <c r="K20" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="87" t="s">
+      <c r="L20" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="87"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="87"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
       <c r="P20" s="38" t="s">
         <v>72</v>
       </c>
@@ -9640,225 +9637,225 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="89"/>
+      <c r="C21" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="I21" s="122" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S21" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="90"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="102"/>
+      <c r="N23" s="102"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="92"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="114" t="s">
+      <c r="B25" s="150"/>
+      <c r="C25" s="151" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="42" t="s">
         <v>201</v>
-      </c>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="I21" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="98" t="s">
-        <v>203</v>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S21" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="106"/>
-      <c r="B22" s="107"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="S22" s="60" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="106"/>
-      <c r="B23" s="107"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="118"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="108"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="122"/>
-      <c r="P24" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="S24" s="60" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="141" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="142"/>
-      <c r="C25" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="D25" s="143"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="42" t="s">
-        <v>202</v>
       </c>
       <c r="I25" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="K25" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="L25" s="111" t="s">
         <v>215</v>
       </c>
-      <c r="L25" s="127" t="s">
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="29" t="s">
+      <c r="Q25" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="R25" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S25" s="63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="138"/>
+      <c r="C26" s="139" t="s">
         <v>217</v>
       </c>
-      <c r="Q25" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="R25" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="S25" s="63" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="144" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" s="145"/>
-      <c r="C26" s="146" t="s">
-        <v>218</v>
-      </c>
-      <c r="D26" s="146"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="146"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
       <c r="H26" s="46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I26" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K26" s="48"/>
-      <c r="L26" s="147"/>
-      <c r="M26" s="148"/>
-      <c r="N26" s="148"/>
-      <c r="O26" s="149"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="142"/>
       <c r="P26" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q26" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="R26" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="R26" s="49" t="s">
+      <c r="S26" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="27" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="150" t="s">
-        <v>222</v>
-      </c>
-      <c r="B27" s="151"/>
-      <c r="C27" s="152" t="s">
-        <v>219</v>
-      </c>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
+      <c r="A27" s="143" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="144"/>
+      <c r="C27" s="145" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="145"/>
       <c r="H27" s="59" t="s">
         <v>49</v>
       </c>
@@ -9866,43 +9863,28 @@
         <v>9</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K27" s="51"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="154"/>
-      <c r="N27" s="154"/>
-      <c r="O27" s="155"/>
+      <c r="L27" s="146"/>
+      <c r="M27" s="147"/>
+      <c r="N27" s="147"/>
+      <c r="O27" s="148"/>
       <c r="P27" s="73" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q27" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R27" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="R27" s="74" t="s">
+      <c r="S27" s="75" t="s">
         <v>191</v>
-      </c>
-      <c r="S27" s="75" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="L21:O24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="C21:G24"/>
-    <mergeCell ref="A21:B24"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="A1:Q1"/>
@@ -9916,6 +9898,21 @@
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K19:O19"/>
     <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="L21:O24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="C21:G24"/>
+    <mergeCell ref="A21:B24"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="L27:O27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B8AB2723-0DBB-4F87-B341-FF92A393E7BB}"/>
@@ -9972,73 +9969,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A9</f>
         <v>UnidadTiempoUso</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B9</f>
         <v>Objeto de dominio que representa una unidad de tiempo encargado de asignar la manera en como se va a medir el tiempo de unos de una persona según las necesidades o claridad de uso para un residente en una zona común .</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -10147,19 +10144,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -10202,24 +10199,24 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>8</v>
@@ -10235,7 +10232,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="27" t="s">
@@ -10257,24 +10254,24 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R7" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S7" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>10</v>
@@ -10290,7 +10287,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J8" s="25"/>
       <c r="K8" s="27"/>
@@ -10310,19 +10307,19 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -10347,7 +10344,7 @@
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L9" s="25" t="s">
         <v>52</v>
@@ -10365,93 +10362,93 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R9" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T9" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U9" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="207" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="207"/>
-      <c r="C11" s="207"/>
+      <c r="A11" s="159" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="159"/>
+      <c r="C11" s="159"/>
     </row>
     <row r="12" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="208" t="s">
+      <c r="A12" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="208" t="s">
+      <c r="B12" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="208" t="s">
+      <c r="C12" s="78" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="64.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="209" t="s">
+      <c r="A13" s="79" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="B13" s="209" t="s">
-        <v>318</v>
-      </c>
-      <c r="C13" s="210" t="s">
+      <c r="C13" s="80" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85" t="s">
+      <c r="B15" s="118"/>
+      <c r="C15" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85" t="s">
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="85"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="85" t="s">
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="L15" s="85"/>
-      <c r="M15" s="85"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="85" t="s">
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="Q15" s="85"/>
-      <c r="R15" s="85" t="s">
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="S15" s="86"/>
+      <c r="S15" s="125"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="97"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
+      <c r="A16" s="136"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
       <c r="H16" s="38" t="s">
         <v>70</v>
       </c>
@@ -10464,12 +10461,12 @@
       <c r="K16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="87" t="s">
+      <c r="L16" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="M16" s="87"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="87"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="126"/>
+      <c r="O16" s="126"/>
       <c r="P16" s="38" t="s">
         <v>72</v>
       </c>
@@ -10484,225 +10481,225 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="89"/>
+      <c r="C17" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="I17" s="122" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S17" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="90"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="S18" s="60" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="90"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="S19" s="60" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="92"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="105"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="S20" s="60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="114" t="s">
+      <c r="B21" s="150"/>
+      <c r="C21" s="151" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="42" t="s">
         <v>201</v>
-      </c>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="I17" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="98" t="s">
-        <v>203</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="116"/>
-      <c r="P17" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q17" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S17" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="106"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="119"/>
-      <c r="P18" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q18" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="R18" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="S18" s="60" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="106"/>
-      <c r="B19" s="107"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="S19" s="60" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="108"/>
-      <c r="B20" s="109"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="120"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="122"/>
-      <c r="P20" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="S20" s="60" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="141" t="s">
-        <v>153</v>
-      </c>
-      <c r="B21" s="142"/>
-      <c r="C21" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="143"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="42" t="s">
-        <v>202</v>
       </c>
       <c r="I21" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="K21" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="L21" s="111" t="s">
         <v>215</v>
       </c>
-      <c r="L21" s="127" t="s">
+      <c r="M21" s="111"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="29" t="s">
+      <c r="Q21" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="R21" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S21" s="63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="138"/>
+      <c r="C22" s="139" t="s">
         <v>217</v>
       </c>
-      <c r="Q21" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="R21" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="S21" s="63" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="144" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="146" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="146"/>
-      <c r="G22" s="146"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
       <c r="H22" s="46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I22" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K22" s="48"/>
-      <c r="L22" s="147"/>
-      <c r="M22" s="148"/>
-      <c r="N22" s="148"/>
-      <c r="O22" s="149"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="141"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="142"/>
       <c r="P22" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q22" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="R22" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="R22" s="49" t="s">
+      <c r="S22" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="S22" s="49" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="150" t="s">
-        <v>222</v>
-      </c>
-      <c r="B23" s="151"/>
-      <c r="C23" s="152" t="s">
-        <v>219</v>
-      </c>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152"/>
+      <c r="A23" s="143" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
       <c r="H23" s="59" t="s">
         <v>49</v>
       </c>
@@ -10710,28 +10707,45 @@
         <v>9</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K23" s="51"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="154"/>
-      <c r="N23" s="154"/>
-      <c r="O23" s="155"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="148"/>
       <c r="P23" s="73" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q23" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R23" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="R23" s="74" t="s">
+      <c r="S23" s="75" t="s">
         <v>191</v>
-      </c>
-      <c r="S23" s="75" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="L17:O20"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:G16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="A17:B20"/>
+    <mergeCell ref="C17:G20"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="J17:J20"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="L23:O23"/>
@@ -10741,23 +10755,6 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A17:B20"/>
-    <mergeCell ref="C17:G20"/>
-    <mergeCell ref="H17:H20"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="L17:O20"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:G16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{3E822B6E-3E69-4872-A72B-64DA54F35712}"/>
@@ -10813,73 +10810,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A5</f>
         <v>Administrador</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B5</f>
         <v>Objeto de dominio que representa el Administrador encargado de hacer la creación o gestión de las zonas comunes y la gestión de residentes y sus respectivas reservas en caso de ser necesario.</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
@@ -10988,19 +10985,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -11043,19 +11040,19 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -11098,24 +11095,24 @@
         <v>52</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>8</v>
@@ -11153,24 +11150,24 @@
         <v>52</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S8" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U8" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T8" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U8" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>13</v>
@@ -11186,11 +11183,11 @@
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
       <c r="I9" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J9" s="25"/>
       <c r="K9" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>52</v>
@@ -11208,24 +11205,24 @@
         <v>52</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R9" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S9" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T9" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U9" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T9" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U9" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>13</v>
@@ -11241,7 +11238,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J10" s="25"/>
       <c r="K10" s="27" t="s">
@@ -11263,24 +11260,24 @@
         <v>52</v>
       </c>
       <c r="Q10" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R10" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U10" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>75</v>
@@ -11316,19 +11313,19 @@
         <v>52</v>
       </c>
       <c r="Q11" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R11" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>184</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U11" s="31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -11369,37 +11366,37 @@
         <v>52</v>
       </c>
       <c r="Q12" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R12" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S12" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U12" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
-      <c r="E15" s="91" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="I15" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="91"/>
-      <c r="K15" s="91"/>
+      <c r="A15" s="130" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="E15" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="I15" s="130" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
@@ -11431,100 +11428,100 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="92" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="92" t="s">
+      <c r="A17" s="131" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="B17" s="131" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="132" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="131" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="131" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="131" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="131" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" s="132" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="131"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="132"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="132"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="132"/>
+    </row>
+    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="131"/>
+      <c r="B19" s="131"/>
+      <c r="C19" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="92" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="92" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="93" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="92"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="93"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="93"/>
-    </row>
-    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="92"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="92"/>
-      <c r="F19" s="92"/>
-      <c r="G19" s="93"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="93"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="132"/>
+      <c r="I19" s="131"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="132"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85" t="s">
+      <c r="B21" s="118"/>
+      <c r="C21" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85" t="s">
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="85"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="85" t="s">
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="L21" s="85"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85"/>
-      <c r="P21" s="85" t="s">
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="Q21" s="85"/>
-      <c r="R21" s="85" t="s">
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="S21" s="86"/>
+      <c r="S21" s="125"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="97"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
+      <c r="A22" s="136"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
       <c r="H22" s="38" t="s">
         <v>70</v>
       </c>
@@ -11537,12 +11534,12 @@
       <c r="K22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="87" t="s">
+      <c r="L22" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="87"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="87"/>
+      <c r="M22" s="126"/>
+      <c r="N22" s="126"/>
+      <c r="O22" s="126"/>
       <c r="P22" s="38" t="s">
         <v>72</v>
       </c>
@@ -11557,175 +11554,175 @@
       </c>
     </row>
     <row r="23" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="114" t="s">
-        <v>243</v>
-      </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="82" t="str">
+      <c r="A23" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="89"/>
+      <c r="C23" s="98" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
       </c>
-      <c r="I23" s="101" t="str">
+      <c r="I23" s="122" t="str">
         <f>B2</f>
         <v>Administrador</v>
       </c>
-      <c r="J23" s="98" t="str">
+      <c r="J23" s="119" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Administrador</v>
       </c>
       <c r="K23" s="16"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="116"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="99"/>
+      <c r="O23" s="100"/>
       <c r="P23" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S23" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="90"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="102"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="Q23" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="R23" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S23" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="106"/>
-      <c r="B24" s="107"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="117"/>
-      <c r="M24" s="118"/>
-      <c r="N24" s="118"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="14" t="s">
+      <c r="R24" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="S24" s="60" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="90"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="102"/>
+      <c r="N25" s="102"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="Q24" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="R24" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="S24" s="60" t="s">
+      <c r="R25" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="S25" s="60" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="106"/>
-      <c r="B25" s="107"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="117"/>
-      <c r="M25" s="118"/>
-      <c r="N25" s="118"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="14" t="s">
+    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="90"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="Q25" s="13" t="s">
+      <c r="Q26" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="S26" s="60" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="105"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q27" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="R27" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="S25" s="60" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="106"/>
-      <c r="B26" s="107"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="118"/>
-      <c r="N26" s="118"/>
-      <c r="O26" s="119"/>
-      <c r="P26" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="S26" s="60" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="121"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="R27" s="13" t="s">
+      <c r="S27" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="S27" s="60" t="s">
+    </row>
+    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="149" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="150"/>
+      <c r="C28" s="151" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="141" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="142"/>
-      <c r="C28" s="143" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="143"/>
-      <c r="E28" s="143"/>
-      <c r="F28" s="143"/>
-      <c r="G28" s="143"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="151"/>
       <c r="H28" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -11739,39 +11736,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de Administrador de un conjunto residencial.</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="L28" s="127" t="s">
-        <v>246</v>
-      </c>
-      <c r="M28" s="127"/>
-      <c r="N28" s="127"/>
-      <c r="O28" s="127"/>
+        <v>214</v>
+      </c>
+      <c r="L28" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
       <c r="P28" s="29" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q28" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R28" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S28" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S28" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="29" spans="1:19" ht="88.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="144" t="s">
-        <v>154</v>
-      </c>
-      <c r="B29" s="145"/>
-      <c r="C29" s="146" t="s">
-        <v>244</v>
-      </c>
-      <c r="D29" s="146"/>
-      <c r="E29" s="146"/>
-      <c r="F29" s="146"/>
-      <c r="G29" s="146"/>
+      <c r="A29" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="138"/>
+      <c r="C29" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
       <c r="H29" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -11785,35 +11782,35 @@
         <v>Corresponde a los datos que se van a modificar de la Administrador</v>
       </c>
       <c r="K29" s="48"/>
-      <c r="L29" s="147"/>
-      <c r="M29" s="148"/>
-      <c r="N29" s="148"/>
-      <c r="O29" s="149"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="142"/>
       <c r="P29" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q29" s="49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R29" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S29" s="49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="150" t="s">
-        <v>222</v>
-      </c>
-      <c r="B30" s="151"/>
-      <c r="C30" s="152" t="s">
-        <v>245</v>
-      </c>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="152"/>
+      <c r="A30" s="143" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="144"/>
+      <c r="C30" s="145" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145"/>
       <c r="H30" s="59" t="s">
         <v>49</v>
       </c>
@@ -11825,46 +11822,25 @@
         <v>Corresponde al identificador del Administrador  que se quiere dar de baja.</v>
       </c>
       <c r="K30" s="51"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="154"/>
-      <c r="N30" s="154"/>
-      <c r="O30" s="155"/>
+      <c r="L30" s="146"/>
+      <c r="M30" s="147"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="148"/>
       <c r="P30" s="73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q30" s="74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R30" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S30" s="75" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="K17:K19"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="L23:O27"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K21:O21"/>
-    <mergeCell ref="A23:B27"/>
-    <mergeCell ref="C23:G27"/>
-    <mergeCell ref="H23:H27"/>
-    <mergeCell ref="I23:I27"/>
-    <mergeCell ref="J23:J27"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="L22:O22"/>
     <mergeCell ref="A1:Q1"/>
@@ -11881,6 +11857,27 @@
     <mergeCell ref="J17:J19"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="G17:G19"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:O21"/>
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="L23:O27"/>
+    <mergeCell ref="A23:B27"/>
+    <mergeCell ref="C23:G27"/>
+    <mergeCell ref="H23:H27"/>
+    <mergeCell ref="I23:I27"/>
+    <mergeCell ref="J23:J27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B1A972F6-B36A-42D4-994E-AD97A6BC793F}"/>
@@ -11941,73 +11938,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A6</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B6</f>
         <v>Objeto de dominio que representa una zona de inmuebles en un conjunto residencial se refiere a una agrupación de unidades habitacionales (torre, bloque, lote) que comparten una ubicación fisica y caracteristicas comunes dentro del conjunto.</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -12062,7 +12059,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A22</f>
@@ -12115,44 +12112,48 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>85</v>
+      <c r="A6" s="53" t="s">
+        <v>86</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" s="25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" s="25">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="G6" s="25">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25">
+        <v>200</v>
+      </c>
       <c r="I6" s="26" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J6" s="25"/>
       <c r="K6" s="27" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="L6" s="28" t="s">
         <v>52</v>
@@ -12173,75 +12174,53 @@
         <v>132</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
-        <v>87</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>85</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="25">
-        <v>1</v>
-      </c>
-      <c r="D7" s="25">
-        <v>20</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
-      <c r="G7" s="25">
-        <v>1</v>
-      </c>
-      <c r="H7" s="25">
-        <v>200</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>81</v>
-      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26"/>
       <c r="J7" s="25"/>
-      <c r="K7" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>52</v>
-      </c>
+      <c r="K7" s="27"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
       <c r="Q7" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R7" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S7" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T7" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U7" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12279,25 +12258,25 @@
         <v>61</v>
       </c>
       <c r="R8" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S8" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="134" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="135"/>
-      <c r="C10" s="136"/>
+      <c r="A10" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="153"/>
+      <c r="C10" s="154"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
@@ -12311,72 +12290,72 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="179" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="139" t="s">
-        <v>134</v>
+      <c r="A12" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="157" t="s">
+        <v>133</v>
       </c>
       <c r="C12" s="70" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="180"/>
-      <c r="B13" s="182"/>
+      <c r="A13" s="178"/>
+      <c r="B13" s="180"/>
       <c r="C13" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="181"/>
-      <c r="B14" s="140"/>
+      <c r="A14" s="179"/>
+      <c r="B14" s="158"/>
       <c r="C14" s="37" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="183" t="s">
+      <c r="A16" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="184"/>
-      <c r="C16" s="187" t="s">
+      <c r="B16" s="182"/>
+      <c r="C16" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="188"/>
-      <c r="E16" s="188"/>
-      <c r="F16" s="188"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="174" t="s">
+      <c r="D16" s="186"/>
+      <c r="E16" s="186"/>
+      <c r="F16" s="186"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="191"/>
-      <c r="J16" s="192"/>
-      <c r="K16" s="174" t="s">
+      <c r="I16" s="189"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="191"/>
-      <c r="M16" s="191"/>
-      <c r="N16" s="191"/>
-      <c r="O16" s="192"/>
-      <c r="P16" s="174" t="s">
+      <c r="L16" s="189"/>
+      <c r="M16" s="189"/>
+      <c r="N16" s="189"/>
+      <c r="O16" s="190"/>
+      <c r="P16" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="Q16" s="192"/>
-      <c r="R16" s="174" t="s">
+      <c r="Q16" s="190"/>
+      <c r="R16" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="S16" s="175"/>
+      <c r="S16" s="173"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="185"/>
-      <c r="B17" s="186"/>
-      <c r="C17" s="189"/>
-      <c r="D17" s="190"/>
-      <c r="E17" s="190"/>
-      <c r="F17" s="190"/>
-      <c r="G17" s="186"/>
+      <c r="A17" s="183"/>
+      <c r="B17" s="184"/>
+      <c r="C17" s="187"/>
+      <c r="D17" s="188"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="184"/>
       <c r="H17" s="38" t="s">
         <v>70</v>
       </c>
@@ -12389,12 +12368,12 @@
       <c r="K17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="176" t="s">
+      <c r="L17" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="177"/>
-      <c r="N17" s="177"/>
-      <c r="O17" s="178"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="175"/>
+      <c r="O17" s="176"/>
       <c r="P17" s="38" t="s">
         <v>72</v>
       </c>
@@ -12409,146 +12388,146 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="193" t="s">
-        <v>152</v>
-      </c>
-      <c r="B18" s="194"/>
-      <c r="C18" s="197" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="198"/>
-      <c r="E18" s="198"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="199"/>
-      <c r="H18" s="82" t="str">
+      <c r="A18" s="160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="161"/>
+      <c r="C18" s="164" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="166"/>
+      <c r="H18" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
       </c>
-      <c r="I18" s="203" t="str">
+      <c r="I18" s="170" t="str">
         <f>B2</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="J18" s="98" t="str">
+      <c r="J18" s="119" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ZonaInmueble</v>
       </c>
       <c r="K18" s="16"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-      <c r="O18" s="116"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="100"/>
       <c r="P18" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q18" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="Q18" s="13" t="s">
+      <c r="R18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S18" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="162"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="167"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="171"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="R18" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S18" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="195"/>
-      <c r="B19" s="196"/>
-      <c r="C19" s="200"/>
-      <c r="D19" s="201"/>
-      <c r="E19" s="201"/>
-      <c r="F19" s="201"/>
-      <c r="G19" s="202"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="204"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="14" t="s">
+      <c r="Q19" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="S19" s="60" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="162"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="168"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="171"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="102"/>
+      <c r="N20" s="102"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="Q19" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="S19" s="60" t="s">
+      <c r="Q20" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="R20" s="13" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="195"/>
-      <c r="B20" s="196"/>
-      <c r="C20" s="200"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="201"/>
-      <c r="G20" s="202"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="204"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="14" t="s">
+      <c r="S20" s="60" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="162"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="168"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="171"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="102"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="Q20" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="S20" s="60" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="195"/>
-      <c r="B21" s="196"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="201"/>
-      <c r="F21" s="201"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="204"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="Q21" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R21" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S21" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" s="162"/>
-      <c r="C22" s="163" t="s">
-        <v>247</v>
-      </c>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="165"/>
+      <c r="A22" s="196" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="197"/>
+      <c r="C22" s="198" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="199"/>
+      <c r="E22" s="199"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="200"/>
       <c r="H22" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
@@ -12562,39 +12541,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de ZonaInmueble de un conjunto residencial.</v>
       </c>
       <c r="K22" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="L22" s="201" t="s">
         <v>215</v>
       </c>
-      <c r="L22" s="166" t="s">
-        <v>216</v>
-      </c>
-      <c r="M22" s="167"/>
-      <c r="N22" s="167"/>
-      <c r="O22" s="168"/>
+      <c r="M22" s="202"/>
+      <c r="N22" s="202"/>
+      <c r="O22" s="203"/>
       <c r="P22" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q22" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R22" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S22" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S22" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="23" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="169" t="s">
-        <v>154</v>
-      </c>
-      <c r="B23" s="170"/>
-      <c r="C23" s="171" t="s">
-        <v>249</v>
-      </c>
-      <c r="D23" s="172"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="172"/>
-      <c r="G23" s="173"/>
+      <c r="A23" s="204" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="205"/>
+      <c r="C23" s="206" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="207"/>
+      <c r="E23" s="207"/>
+      <c r="F23" s="207"/>
+      <c r="G23" s="208"/>
       <c r="H23" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
@@ -12608,35 +12587,35 @@
         <v>Corresponde a los datos que se van a modificar de la ZonaInmueble</v>
       </c>
       <c r="K23" s="48"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="148"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="149"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="141"/>
+      <c r="N23" s="141"/>
+      <c r="O23" s="142"/>
       <c r="P23" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q23" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R23" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S23" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="156" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" s="157"/>
-      <c r="C24" s="158" t="s">
-        <v>250</v>
-      </c>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="160"/>
+      <c r="A24" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" s="192"/>
+      <c r="C24" s="193" t="s">
+        <v>249</v>
+      </c>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="195"/>
       <c r="H24" s="59" t="s">
         <v>49</v>
       </c>
@@ -12648,31 +12627,34 @@
         <v>Corresponde al identificador de la ZonaInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K24" s="51"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="154"/>
-      <c r="N24" s="154"/>
-      <c r="O24" s="155"/>
+      <c r="L24" s="146"/>
+      <c r="M24" s="147"/>
+      <c r="N24" s="147"/>
+      <c r="O24" s="148"/>
       <c r="P24" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S24" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="L18:O21"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C18:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="A1:Q1"/>
@@ -12686,15 +12668,12 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="K16:O16"/>
     <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="L18:O21"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="C18:G21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{00F0F8F7-DC0F-4454-B174-288E79B7BE78}"/>
@@ -12752,73 +12731,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="128" t="str">
         <f>'Listado Objetos Dominio'!A8</f>
         <v>TipoZonaInmueble</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="129" t="str">
         <f>'Listado Objetos Dominio'!B8</f>
         <v>Objeto de dominio que representa un tipo de zona inmueble encargado de hacer la creación de nuevas zonas inmuebles para el conjunto residencial como torres, bloques , manzanas etc .</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
@@ -12873,7 +12852,7 @@
         <v>3</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S4" s="66" t="str">
         <f>A18</f>
@@ -12926,19 +12905,19 @@
         <v>51</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R5" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -12979,94 +12958,94 @@
         <v>52</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R6" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="T6" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="207" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="207"/>
-      <c r="C8" s="207"/>
+      <c r="A8" s="159" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
     </row>
     <row r="9" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="208" t="s">
+      <c r="B9" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="78" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="55.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="209" t="s">
+      <c r="A10" s="79" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="209" t="s">
-        <v>324</v>
-      </c>
-      <c r="C10" s="210" t="str">
+      <c r="C10" s="80" t="str">
         <f>A6</f>
         <v>nombre</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="187" t="s">
+      <c r="B12" s="182"/>
+      <c r="C12" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="188"/>
-      <c r="E12" s="188"/>
-      <c r="F12" s="188"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="174" t="s">
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="182"/>
+      <c r="H12" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="191"/>
-      <c r="J12" s="192"/>
-      <c r="K12" s="174" t="s">
+      <c r="I12" s="189"/>
+      <c r="J12" s="190"/>
+      <c r="K12" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="L12" s="191"/>
-      <c r="M12" s="191"/>
-      <c r="N12" s="191"/>
-      <c r="O12" s="192"/>
-      <c r="P12" s="174" t="s">
+      <c r="L12" s="189"/>
+      <c r="M12" s="189"/>
+      <c r="N12" s="189"/>
+      <c r="O12" s="190"/>
+      <c r="P12" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="Q12" s="192"/>
-      <c r="R12" s="174" t="s">
+      <c r="Q12" s="190"/>
+      <c r="R12" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="S12" s="175"/>
+      <c r="S12" s="173"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="185"/>
-      <c r="B13" s="186"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="186"/>
+      <c r="A13" s="183"/>
+      <c r="B13" s="184"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="188"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="184"/>
       <c r="H13" s="38" t="s">
         <v>70</v>
       </c>
@@ -13079,12 +13058,12 @@
       <c r="K13" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="176" t="s">
+      <c r="L13" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="177"/>
-      <c r="N13" s="177"/>
-      <c r="O13" s="178"/>
+      <c r="M13" s="175"/>
+      <c r="N13" s="175"/>
+      <c r="O13" s="176"/>
       <c r="P13" s="38" t="s">
         <v>72</v>
       </c>
@@ -13099,146 +13078,146 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="194"/>
-      <c r="C14" s="197" t="s">
-        <v>248</v>
-      </c>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="198"/>
-      <c r="G14" s="199"/>
-      <c r="H14" s="82" t="str">
+      <c r="A14" s="160" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="161"/>
+      <c r="C14" s="164" t="s">
+        <v>247</v>
+      </c>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="166"/>
+      <c r="H14" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
       </c>
-      <c r="I14" s="203" t="str">
+      <c r="I14" s="170" t="str">
         <f>B2</f>
         <v>TipoZonaInmueble</v>
       </c>
-      <c r="J14" s="98" t="str">
+      <c r="J14" s="119" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva TipoZonaInmueble</v>
       </c>
       <c r="K14" s="16"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="116"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="100"/>
       <c r="P14" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q14" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="Q14" s="13" t="s">
+      <c r="R14" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="S14" s="60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="162"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="167"/>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="169"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="103"/>
+      <c r="P15" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="R14" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="S14" s="60" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="195"/>
-      <c r="B15" s="196"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
-      <c r="F15" s="201"/>
-      <c r="G15" s="202"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="204"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="14" t="s">
+      <c r="Q15" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="S15" s="60" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="102"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="Q15" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="S15" s="60" t="s">
+      <c r="Q16" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="R16" s="13" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="195"/>
-      <c r="B16" s="196"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="201"/>
-      <c r="G16" s="202"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="204"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="14" t="s">
+      <c r="S16" s="60" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="162"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="171"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="102"/>
+      <c r="N17" s="102"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="Q16" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="R16" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="S16" s="60" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="195"/>
-      <c r="B17" s="196"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="204"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="118"/>
-      <c r="N17" s="118"/>
-      <c r="O17" s="119"/>
-      <c r="P17" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="Q17" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S17" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="B18" s="162"/>
-      <c r="C18" s="163" t="s">
-        <v>247</v>
-      </c>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="A18" s="196" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="197"/>
+      <c r="C18" s="198" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18" s="199"/>
+      <c r="E18" s="199"/>
+      <c r="F18" s="199"/>
+      <c r="G18" s="200"/>
       <c r="H18" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
@@ -13252,39 +13231,39 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de TipoZonaInmueble de un conjunto residencial.</v>
       </c>
       <c r="K18" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="L18" s="201" t="s">
         <v>215</v>
       </c>
-      <c r="L18" s="166" t="s">
-        <v>216</v>
-      </c>
-      <c r="M18" s="167"/>
-      <c r="N18" s="167"/>
-      <c r="O18" s="168"/>
+      <c r="M18" s="202"/>
+      <c r="N18" s="202"/>
+      <c r="O18" s="203"/>
       <c r="P18" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q18" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R18" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="S18" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="S18" s="63" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="19" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="169" t="s">
-        <v>154</v>
-      </c>
-      <c r="B19" s="170"/>
-      <c r="C19" s="171" t="s">
-        <v>249</v>
-      </c>
-      <c r="D19" s="172"/>
-      <c r="E19" s="172"/>
-      <c r="F19" s="172"/>
-      <c r="G19" s="173"/>
+      <c r="A19" s="204" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="205"/>
+      <c r="C19" s="206" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="207"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="207"/>
+      <c r="G19" s="208"/>
       <c r="H19" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
@@ -13298,35 +13277,35 @@
         <v>Corresponde a los datos que se van a modificar de la TipoZonaInmueble</v>
       </c>
       <c r="K19" s="48"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="148"/>
-      <c r="N19" s="148"/>
-      <c r="O19" s="149"/>
+      <c r="L19" s="140"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="141"/>
+      <c r="O19" s="142"/>
       <c r="P19" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q19" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R19" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S19" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="156" t="s">
-        <v>222</v>
-      </c>
-      <c r="B20" s="157"/>
-      <c r="C20" s="158" t="s">
-        <v>250</v>
-      </c>
-      <c r="D20" s="159"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="160"/>
+      <c r="A20" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="192"/>
+      <c r="C20" s="193" t="s">
+        <v>249</v>
+      </c>
+      <c r="D20" s="194"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="194"/>
+      <c r="G20" s="195"/>
       <c r="H20" s="59" t="s">
         <v>49</v>
       </c>
@@ -13338,25 +13317,42 @@
         <v>Corresponde al identificador de la TipoZonaInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K20" s="51"/>
-      <c r="L20" s="153"/>
-      <c r="M20" s="154"/>
-      <c r="N20" s="154"/>
-      <c r="O20" s="155"/>
+      <c r="L20" s="146"/>
+      <c r="M20" s="147"/>
+      <c r="N20" s="147"/>
+      <c r="O20" s="148"/>
       <c r="P20" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R20" s="52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S20" s="52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="L14:O17"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:G13"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:O12"/>
+    <mergeCell ref="A14:B17"/>
+    <mergeCell ref="C14:G17"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="I14:I17"/>
+    <mergeCell ref="J14:J17"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="L20:O20"/>
@@ -13366,23 +13362,6 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A14:B17"/>
-    <mergeCell ref="C14:G17"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="I14:I17"/>
-    <mergeCell ref="J14:J17"/>
-    <mergeCell ref="L14:O17"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:G13"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="K12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{ADA2A2A6-5B57-4F87-8E96-63F5687CC6C2}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73450C3-3A49-49B0-A7B5-446B11AA43DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB66F9C-81DE-43AD-BC21-A661F9C1709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20805" yWindow="2265" windowWidth="18045" windowHeight="15345" firstSheet="7" activeTab="10" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
+    <workbookView xWindow="1290" yWindow="2040" windowWidth="17340" windowHeight="15345" firstSheet="3" activeTab="4" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3478,7 +3478,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="324">
   <si>
     <t>Referenciado</t>
   </si>
@@ -8179,7 +8179,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="25">
         <v>50</v>
@@ -10225,7 +10225,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
@@ -10277,10 +10277,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" s="25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
@@ -10339,13 +10339,9 @@
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="26" t="s">
-        <v>57</v>
-      </c>
+      <c r="I9" s="26"/>
       <c r="J9" s="25"/>
-      <c r="K9" s="27" t="s">
-        <v>295</v>
-      </c>
+      <c r="K9" s="27"/>
       <c r="L9" s="25" t="s">
         <v>52</v>
       </c>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo Dominio Enriquecido ConjuntosResidenciales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB66F9C-81DE-43AD-BC21-A661F9C1709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5EB946-0B11-471F-AA45-FD12BFC5B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="2040" windowWidth="17340" windowHeight="15345" firstSheet="3" activeTab="4" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{68A10BBB-2615-4E9A-8951-B88AC10A8A21}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3478,7 +3478,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="324">
   <si>
     <t>Referenciado</t>
   </si>
@@ -5443,6 +5443,63 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5533,62 +5590,35 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5626,39 +5656,120 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5694,117 +5805,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6214,19 +6214,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E67951-2C7D-49B7-A34C-4F3BE877730E}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="82"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -6250,52 +6250,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -6311,103 +6311,103 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EB456-CB79-4A40-96E9-87554CA83EDD}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.28515625" style="76" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="76" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A7</f>
         <v>TipoInmueble</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B7</f>
         <v>Objeto de dominio que representa un tipo de inmueble encargado de hacer la creación de nuevos tipos inmuebles para el conjunto residencial como casas, apartamentos, glamplins  etc .</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>53</v>
       </c>
@@ -6581,14 +6581,14 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="130" t="s">
+    <row r="8" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>63</v>
       </c>
@@ -6599,65 +6599,65 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="131" t="s">
+    <row r="10" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="95" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="132" t="str">
+      <c r="C10" s="96" t="str">
         <f>A6</f>
         <v>nombre</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="131"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="132"/>
-    </row>
-    <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+    <row r="11" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="95"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="96"/>
+    </row>
+    <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="182"/>
-      <c r="C13" s="185" t="s">
+      <c r="B13" s="188"/>
+      <c r="C13" s="191" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-      <c r="F13" s="186"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="172" t="s">
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="188"/>
+      <c r="H13" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="189"/>
-      <c r="J13" s="190"/>
-      <c r="K13" s="172" t="s">
+      <c r="I13" s="195"/>
+      <c r="J13" s="196"/>
+      <c r="K13" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="189"/>
-      <c r="M13" s="189"/>
-      <c r="N13" s="189"/>
-      <c r="O13" s="190"/>
-      <c r="P13" s="172" t="s">
+      <c r="L13" s="195"/>
+      <c r="M13" s="195"/>
+      <c r="N13" s="195"/>
+      <c r="O13" s="196"/>
+      <c r="P13" s="178" t="s">
         <v>68</v>
       </c>
-      <c r="Q13" s="190"/>
-      <c r="R13" s="172" t="s">
+      <c r="Q13" s="196"/>
+      <c r="R13" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="S13" s="173"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="183"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="187"/>
-      <c r="D14" s="188"/>
-      <c r="E14" s="188"/>
-      <c r="F14" s="188"/>
-      <c r="G14" s="184"/>
+      <c r="S13" s="179"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="189"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+      <c r="F14" s="194"/>
+      <c r="G14" s="190"/>
       <c r="H14" s="77" t="s">
         <v>70</v>
       </c>
@@ -6670,12 +6670,12 @@
       <c r="K14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="174" t="s">
+      <c r="L14" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="175"/>
-      <c r="N14" s="175"/>
-      <c r="O14" s="176"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="182"/>
       <c r="P14" s="38" t="s">
         <v>72</v>
       </c>
@@ -6689,35 +6689,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="160" t="s">
+    <row r="15" spans="1:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="197" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="161"/>
-      <c r="C15" s="164" t="s">
+      <c r="B15" s="198"/>
+      <c r="C15" s="201" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="165"/>
-      <c r="G15" s="166"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="202"/>
+      <c r="G15" s="203"/>
       <c r="H15" s="209" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
       </c>
-      <c r="I15" s="170" t="str">
+      <c r="I15" s="207" t="str">
         <f>B2</f>
         <v>TipoInmueble</v>
       </c>
-      <c r="J15" s="119" t="str">
+      <c r="J15" s="101" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva TipoInmueble</v>
       </c>
       <c r="K15" s="16"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="100"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="119"/>
       <c r="P15" s="14" t="s">
         <v>270</v>
       </c>
@@ -6731,22 +6731,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="169"/>
+    <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="199"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="205"/>
+      <c r="F16" s="205"/>
+      <c r="G16" s="206"/>
       <c r="H16" s="210"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="120"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="102"/>
       <c r="K16" s="61"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="103"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="122"/>
       <c r="P16" s="14" t="s">
         <v>271</v>
       </c>
@@ -6760,22 +6760,22 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="169"/>
+    <row r="17" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="199"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="205"/>
+      <c r="E17" s="205"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="206"/>
       <c r="H17" s="210"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="120"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="102"/>
       <c r="K17" s="61"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="103"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="122"/>
       <c r="P17" s="14" t="s">
         <v>272</v>
       </c>
@@ -6789,22 +6789,22 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="162"/>
-      <c r="B18" s="163"/>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="169"/>
+    <row r="18" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="199"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="204"/>
+      <c r="D18" s="205"/>
+      <c r="E18" s="205"/>
+      <c r="F18" s="205"/>
+      <c r="G18" s="206"/>
       <c r="H18" s="210"/>
-      <c r="I18" s="171"/>
-      <c r="J18" s="120"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="102"/>
       <c r="K18" s="61"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="103"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="122"/>
       <c r="P18" s="14" t="s">
         <v>273</v>
       </c>
@@ -6818,18 +6818,18 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="196" t="s">
+    <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="165" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="197"/>
-      <c r="C19" s="198" t="s">
+      <c r="B19" s="166"/>
+      <c r="C19" s="167" t="s">
         <v>266</v>
       </c>
-      <c r="D19" s="199"/>
-      <c r="E19" s="199"/>
-      <c r="F19" s="199"/>
-      <c r="G19" s="200"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="169"/>
       <c r="H19" s="41" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
@@ -6845,12 +6845,12 @@
       <c r="K19" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L19" s="201" t="s">
+      <c r="L19" s="170" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="202"/>
-      <c r="N19" s="202"/>
-      <c r="O19" s="203"/>
+      <c r="M19" s="171"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="172"/>
       <c r="P19" s="29" t="s">
         <v>286</v>
       </c>
@@ -6864,18 +6864,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="204" t="s">
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="173" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="205"/>
-      <c r="C20" s="206" t="s">
+      <c r="B20" s="174"/>
+      <c r="C20" s="175" t="s">
         <v>267</v>
       </c>
-      <c r="D20" s="207"/>
-      <c r="E20" s="207"/>
-      <c r="F20" s="207"/>
-      <c r="G20" s="208"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="177"/>
       <c r="H20" s="45" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoInmueble</v>
@@ -6889,10 +6889,10 @@
         <v>Corresponde a los datos que se van a modificar de la TipoInmueble</v>
       </c>
       <c r="K20" s="48"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="142"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="151"/>
+      <c r="N20" s="151"/>
+      <c r="O20" s="152"/>
       <c r="P20" s="69" t="s">
         <v>287</v>
       </c>
@@ -6906,18 +6906,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="191" t="s">
+    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="160" t="s">
         <v>221</v>
       </c>
-      <c r="B21" s="192"/>
-      <c r="C21" s="193" t="s">
+      <c r="B21" s="161"/>
+      <c r="C21" s="162" t="s">
         <v>268</v>
       </c>
-      <c r="D21" s="194"/>
-      <c r="E21" s="194"/>
-      <c r="F21" s="194"/>
-      <c r="G21" s="195"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="164"/>
       <c r="H21" s="50" t="s">
         <v>49</v>
       </c>
@@ -6929,10 +6929,10 @@
         <v>Corresponde al identificador de la TipoInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K21" s="51"/>
-      <c r="L21" s="146"/>
-      <c r="M21" s="147"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="148"/>
+      <c r="L21" s="156"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="158"/>
       <c r="P21" s="31" t="s">
         <v>287</v>
       </c>
@@ -6948,6 +6948,25 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="L15:O18"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:G14"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:O13"/>
+    <mergeCell ref="A15:B18"/>
+    <mergeCell ref="C15:G18"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="J15:J18"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="R13:S13"/>
     <mergeCell ref="L14:O14"/>
@@ -6958,25 +6977,6 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="L15:O18"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="C13:G14"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:O13"/>
-    <mergeCell ref="A15:B18"/>
-    <mergeCell ref="C15:G18"/>
-    <mergeCell ref="H15:H18"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="L20:O20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{D07C8615-2E2B-411D-8DD3-94AE21459CC4}"/>
@@ -7004,103 +7004,103 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DC4352-D389-4296-8885-24C883779FA5}">
   <dimension ref="A1:U25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.28515625" style="76" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="76" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A10</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B10</f>
         <v>Objeto de dominio que representa un imnueble dentro de una zona de inmuebles en un conjunto residencial describe las caracteristicas especificasde una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona inmueble.</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>90</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>89</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>27</v>
       </c>
@@ -7346,14 +7346,14 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="130" t="s">
+    <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>63</v>
       </c>
@@ -7364,78 +7364,78 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="131" t="s">
+    <row r="12" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="131" t="s">
+      <c r="B12" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="132" t="s">
+      <c r="C12" s="96" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="131"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="132"/>
-    </row>
-    <row r="14" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="131"/>
-      <c r="B14" s="131"/>
+    <row r="13" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="95"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="96"/>
+    </row>
+    <row r="14" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="95"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="57" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="131"/>
-      <c r="B15" s="131"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="95"/>
+      <c r="B15" s="95"/>
       <c r="C15" s="57" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="181" t="s">
+    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="182"/>
-      <c r="C17" s="185" t="s">
+      <c r="B17" s="188"/>
+      <c r="C17" s="191" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="186"/>
-      <c r="E17" s="186"/>
-      <c r="F17" s="186"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="172" t="s">
+      <c r="D17" s="192"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="192"/>
+      <c r="G17" s="188"/>
+      <c r="H17" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="189"/>
-      <c r="J17" s="190"/>
-      <c r="K17" s="172" t="s">
+      <c r="I17" s="195"/>
+      <c r="J17" s="196"/>
+      <c r="K17" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="189"/>
-      <c r="M17" s="189"/>
-      <c r="N17" s="189"/>
-      <c r="O17" s="190"/>
-      <c r="P17" s="172" t="s">
+      <c r="L17" s="195"/>
+      <c r="M17" s="195"/>
+      <c r="N17" s="195"/>
+      <c r="O17" s="196"/>
+      <c r="P17" s="178" t="s">
         <v>68</v>
       </c>
-      <c r="Q17" s="190"/>
-      <c r="R17" s="172" t="s">
+      <c r="Q17" s="196"/>
+      <c r="R17" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="S17" s="173"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="183"/>
-      <c r="B18" s="184"/>
-      <c r="C18" s="187"/>
-      <c r="D18" s="188"/>
-      <c r="E18" s="188"/>
-      <c r="F18" s="188"/>
-      <c r="G18" s="184"/>
+      <c r="S17" s="179"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="189"/>
+      <c r="B18" s="190"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="194"/>
+      <c r="G18" s="190"/>
       <c r="H18" s="77" t="s">
         <v>70</v>
       </c>
@@ -7448,12 +7448,12 @@
       <c r="K18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="174" t="s">
+      <c r="L18" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="175"/>
-      <c r="N18" s="175"/>
-      <c r="O18" s="176"/>
+      <c r="M18" s="181"/>
+      <c r="N18" s="181"/>
+      <c r="O18" s="182"/>
       <c r="P18" s="38" t="s">
         <v>72</v>
       </c>
@@ -7467,35 +7467,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="160" t="s">
+    <row r="19" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="197" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="161"/>
-      <c r="C19" s="164" t="s">
+      <c r="B19" s="198"/>
+      <c r="C19" s="201" t="s">
         <v>265</v>
       </c>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="165"/>
-      <c r="G19" s="166"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="202"/>
+      <c r="G19" s="203"/>
       <c r="H19" s="209" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I19" s="170" t="str">
+      <c r="I19" s="207" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J19" s="119" t="str">
+      <c r="J19" s="101" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K19" s="16"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="100"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="119"/>
       <c r="P19" s="14" t="s">
         <v>270</v>
       </c>
@@ -7509,22 +7509,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="162"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="167"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="169"/>
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="199"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="204"/>
+      <c r="D20" s="205"/>
+      <c r="E20" s="205"/>
+      <c r="F20" s="205"/>
+      <c r="G20" s="206"/>
       <c r="H20" s="210"/>
-      <c r="I20" s="171"/>
-      <c r="J20" s="120"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="102"/>
       <c r="K20" s="61"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="102"/>
-      <c r="N20" s="102"/>
-      <c r="O20" s="103"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="122"/>
       <c r="P20" s="14" t="s">
         <v>271</v>
       </c>
@@ -7538,22 +7538,22 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="162"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="167"/>
-      <c r="D21" s="168"/>
-      <c r="E21" s="168"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="169"/>
+    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="199"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="204"/>
+      <c r="D21" s="205"/>
+      <c r="E21" s="205"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="206"/>
       <c r="H21" s="210"/>
-      <c r="I21" s="171"/>
-      <c r="J21" s="120"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="102"/>
       <c r="K21" s="61"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="122"/>
       <c r="P21" s="14" t="s">
         <v>272</v>
       </c>
@@ -7567,22 +7567,22 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="162"/>
-      <c r="B22" s="163"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="169"/>
+    <row r="22" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="199"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="204"/>
+      <c r="D22" s="205"/>
+      <c r="E22" s="205"/>
+      <c r="F22" s="205"/>
+      <c r="G22" s="206"/>
       <c r="H22" s="210"/>
-      <c r="I22" s="171"/>
-      <c r="J22" s="120"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="102"/>
       <c r="K22" s="61"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="103"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="122"/>
       <c r="P22" s="14" t="s">
         <v>273</v>
       </c>
@@ -7596,18 +7596,18 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="196" t="s">
+    <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="165" t="s">
         <v>152</v>
       </c>
-      <c r="B23" s="197"/>
-      <c r="C23" s="198" t="s">
+      <c r="B23" s="166"/>
+      <c r="C23" s="167" t="s">
         <v>266</v>
       </c>
-      <c r="D23" s="199"/>
-      <c r="E23" s="199"/>
-      <c r="F23" s="199"/>
-      <c r="G23" s="200"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="169"/>
       <c r="H23" s="41" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -7623,12 +7623,12 @@
       <c r="K23" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L23" s="201" t="s">
+      <c r="L23" s="170" t="s">
         <v>269</v>
       </c>
-      <c r="M23" s="202"/>
-      <c r="N23" s="202"/>
-      <c r="O23" s="203"/>
+      <c r="M23" s="171"/>
+      <c r="N23" s="171"/>
+      <c r="O23" s="172"/>
       <c r="P23" s="29" t="s">
         <v>286</v>
       </c>
@@ -7642,18 +7642,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="204" t="s">
+    <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="173" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="205"/>
-      <c r="C24" s="206" t="s">
+      <c r="B24" s="174"/>
+      <c r="C24" s="175" t="s">
         <v>267</v>
       </c>
-      <c r="D24" s="207"/>
-      <c r="E24" s="207"/>
-      <c r="F24" s="207"/>
-      <c r="G24" s="208"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="177"/>
       <c r="H24" s="45" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -7667,10 +7667,10 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K24" s="48"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="141"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="142"/>
+      <c r="L24" s="150"/>
+      <c r="M24" s="151"/>
+      <c r="N24" s="151"/>
+      <c r="O24" s="152"/>
       <c r="P24" s="69" t="s">
         <v>287</v>
       </c>
@@ -7684,18 +7684,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="191" t="s">
+    <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="160" t="s">
         <v>221</v>
       </c>
-      <c r="B25" s="192"/>
-      <c r="C25" s="193" t="s">
+      <c r="B25" s="161"/>
+      <c r="C25" s="162" t="s">
         <v>268</v>
       </c>
-      <c r="D25" s="194"/>
-      <c r="E25" s="194"/>
-      <c r="F25" s="194"/>
-      <c r="G25" s="195"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="163"/>
+      <c r="F25" s="163"/>
+      <c r="G25" s="164"/>
       <c r="H25" s="50" t="s">
         <v>49</v>
       </c>
@@ -7707,10 +7707,10 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="51"/>
-      <c r="L25" s="146"/>
-      <c r="M25" s="147"/>
-      <c r="N25" s="147"/>
-      <c r="O25" s="148"/>
+      <c r="L25" s="156"/>
+      <c r="M25" s="157"/>
+      <c r="N25" s="157"/>
+      <c r="O25" s="158"/>
       <c r="P25" s="31" t="s">
         <v>287</v>
       </c>
@@ -7726,15 +7726,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L19:O22"/>
+    <mergeCell ref="A19:B22"/>
+    <mergeCell ref="C19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="A1:Q1"/>
@@ -7749,12 +7746,15 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="K17:O17"/>
     <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="L19:O22"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="C19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{E9339FF0-C25B-4ACF-BE04-E905DF5A13F0}"/>
@@ -7783,7 +7783,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B48565E2-FD1C-4C9E-98B4-73DD04C334A2}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7793,16 +7793,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBAC759-F791-4517-AB32-98FD0721A1C2}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="8"/>
+    <col min="1" max="1" width="21.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
@@ -7812,7 +7812,7 @@
       <c r="C1" s="83"/>
       <c r="D1" s="84"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>18</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>Residentes</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>23</v>
       </c>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D4" s="86"/>
     </row>
-    <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>25</v>
       </c>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D5" s="86"/>
     </row>
-    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>27</v>
       </c>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D6" s="86"/>
     </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>302</v>
       </c>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="D7" s="86"/>
     </row>
-    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>303</v>
       </c>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D8" s="86"/>
     </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>299</v>
       </c>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="D9" s="86"/>
     </row>
-    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>20</v>
       </c>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D10" s="87"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7953,103 +7953,103 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52572D8B-2E5B-40A3-93D4-C6D8A4DFB5A3}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.5546875" style="8" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.7109375" style="8" customWidth="1"/>
-    <col min="19" max="19" width="25.140625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.6640625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="25.109375" style="8" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A3</f>
         <v>ConjuntoResidencial</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B3</f>
         <v>Objeto de dominio que representa cada una de las comunidades habitacionales organizadas en un sistema. Abarca la totalidad de los elementos que componen el conjunto, desde las unidades habitacionales individuales (inmuebles) hasta las zonas comunes.</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>53</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>117</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>77</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>116</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>56</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>79</v>
       </c>
@@ -8489,19 +8489,19 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="130" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="130"/>
-      <c r="E13" s="130" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="E13" s="94" t="s">
         <v>129</v>
       </c>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
         <v>63</v>
       </c>
@@ -8521,79 +8521,79 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="131" t="s">
+    <row r="15" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="95" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="132" t="s">
+      <c r="C15" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="131" t="s">
+      <c r="E15" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="F15" s="131" t="s">
+      <c r="F15" s="95" t="s">
         <v>127</v>
       </c>
-      <c r="G15" s="133" t="s">
+      <c r="G15" s="97" t="s">
         <v>116</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="131"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="132"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="134"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
+    <row r="16" spans="1:21" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="95"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="98"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118" t="s">
+      <c r="B18" s="88"/>
+      <c r="C18" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118" t="s">
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118" t="s">
+      <c r="I18" s="88"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118" t="s">
+      <c r="L18" s="88"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118" t="s">
+      <c r="Q18" s="88"/>
+      <c r="R18" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="S18" s="125"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="136"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
+      <c r="S18" s="89"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="100"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
       <c r="H19" s="38" t="s">
         <v>70</v>
       </c>
@@ -8606,12 +8606,12 @@
       <c r="K19" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="126" t="s">
+      <c r="L19" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
       <c r="P19" s="38" t="s">
         <v>72</v>
       </c>
@@ -8625,32 +8625,32 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+    <row r="20" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="98" t="s">
+      <c r="B20" s="108"/>
+      <c r="C20" s="117" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="100"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="119"/>
       <c r="H20" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="119" t="s">
+      <c r="J20" s="101" t="s">
         <v>158</v>
       </c>
       <c r="K20" s="16"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="99"/>
-      <c r="O20" s="100"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="14" t="s">
         <v>160</v>
       </c>
@@ -8664,22 +8664,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="103"/>
+    <row r="21" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="109"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="122"/>
       <c r="H21" s="86"/>
-      <c r="I21" s="123"/>
-      <c r="J21" s="120"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="102"/>
       <c r="K21" s="61"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="122"/>
       <c r="P21" s="14" t="s">
         <v>161</v>
       </c>
@@ -8693,22 +8693,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="90"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="103"/>
+    <row r="22" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="109"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="122"/>
       <c r="H22" s="86"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="120"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="102"/>
       <c r="K22" s="61"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="103"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="122"/>
       <c r="P22" s="14" t="s">
         <v>162</v>
       </c>
@@ -8722,22 +8722,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="106"/>
+    <row r="23" spans="1:19" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="111"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="125"/>
       <c r="H23" s="87"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="121"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="103"/>
       <c r="K23" s="62"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="106"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="124"/>
+      <c r="N23" s="124"/>
+      <c r="O23" s="125"/>
       <c r="P23" s="14" t="s">
         <v>163</v>
       </c>
@@ -8751,18 +8751,18 @@
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="109" t="s">
+    <row r="24" spans="1:19" ht="148.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="128" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="110"/>
-      <c r="C24" s="111" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="130" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
       <c r="H24" s="42" t="s">
         <v>157</v>
       </c>
@@ -8775,12 +8775,12 @@
       <c r="K24" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="L24" s="111" t="s">
+      <c r="L24" s="130" t="s">
         <v>172</v>
       </c>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
+      <c r="M24" s="130"/>
+      <c r="N24" s="130"/>
+      <c r="O24" s="130"/>
       <c r="P24" s="29" t="s">
         <v>187</v>
       </c>
@@ -8794,18 +8794,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="112" t="s">
+    <row r="25" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="131" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="114" t="s">
+      <c r="B25" s="132"/>
+      <c r="C25" s="133" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
       <c r="H25" s="46" t="s">
         <v>157</v>
       </c>
@@ -8816,35 +8816,35 @@
         <v>178</v>
       </c>
       <c r="K25" s="48"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="107" t="s">
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="Q25" s="94" t="s">
+      <c r="Q25" s="113" t="s">
         <v>189</v>
       </c>
-      <c r="R25" s="94" t="s">
+      <c r="R25" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="S25" s="96" t="s">
+      <c r="S25" s="115" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="115" t="s">
+    <row r="26" spans="1:19" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="134" t="s">
         <v>221</v>
       </c>
-      <c r="B26" s="116"/>
-      <c r="C26" s="117" t="s">
+      <c r="B26" s="135"/>
+      <c r="C26" s="136" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
       <c r="H26" s="59" t="s">
         <v>49</v>
       </c>
@@ -8855,17 +8855,38 @@
         <v>176</v>
       </c>
       <c r="K26" s="51"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="117"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="108"/>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="95"/>
-      <c r="S26" s="97"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="127"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A20:B23"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="L20:O23"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="C20:G23"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="K18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="J20:J23"/>
+    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="H20:H23"/>
     <mergeCell ref="R18:S18"/>
     <mergeCell ref="L19:O19"/>
     <mergeCell ref="A1:Q1"/>
@@ -8882,27 +8903,6 @@
     <mergeCell ref="A18:B19"/>
     <mergeCell ref="C18:G19"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="J20:J23"/>
-    <mergeCell ref="I20:I23"/>
-    <mergeCell ref="H20:H23"/>
-    <mergeCell ref="A20:B23"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="L20:O23"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="C20:G23"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="L26:O26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{193F65CD-468D-4EE9-B635-8067A5B8EAA9}"/>
@@ -8929,103 +8929,103 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC27993B-5D8F-4859-AF5A-93E173C14E9E}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.7109375" style="8" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.42578125" style="8" customWidth="1"/>
-    <col min="21" max="21" width="25.42578125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.6640625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.44140625" style="8" customWidth="1"/>
+    <col min="21" max="21" width="25.44140625" style="8" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A4</f>
         <v>ZonaComun</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B4</f>
         <v>Objeto de dominio que representa a cada una de las zonas comunes que se encuentran dentro de un conjunto residencial para que los residentes puedan reservar esos espacios y poder usarlos.</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>53</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>56</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>139</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>140</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>58</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>141</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="32" t="s">
         <v>60</v>
       </c>
@@ -9526,15 +9526,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+    <row r="13" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="154"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="138"/>
+      <c r="C14" s="139"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>63</v>
       </c>
@@ -9545,66 +9545,66 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155" t="s">
+    <row r="16" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="140" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="157" t="s">
+      <c r="B16" s="142" t="s">
         <v>150</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="156"/>
-      <c r="B17" s="158"/>
+    <row r="17" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="141"/>
+      <c r="B17" s="143"/>
       <c r="C17" s="37" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="135" t="s">
+    <row r="18" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="118"/>
-      <c r="C19" s="118" t="s">
+      <c r="B19" s="88"/>
+      <c r="C19" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118" t="s">
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118" t="s">
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="118" t="s">
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="Q19" s="118"/>
-      <c r="R19" s="118" t="s">
+      <c r="Q19" s="88"/>
+      <c r="R19" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="S19" s="125"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="136"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
+      <c r="S19" s="89"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="100"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
       <c r="H20" s="38" t="s">
         <v>70</v>
       </c>
@@ -9617,12 +9617,12 @@
       <c r="K20" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="126" t="s">
+      <c r="L20" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
       <c r="P20" s="38" t="s">
         <v>72</v>
       </c>
@@ -9636,32 +9636,32 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="88" t="s">
+    <row r="21" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="98" t="s">
+      <c r="B21" s="108"/>
+      <c r="C21" s="117" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="100"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="119"/>
       <c r="H21" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="119" t="s">
+      <c r="J21" s="101" t="s">
         <v>202</v>
       </c>
       <c r="K21" s="16"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="100"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="119"/>
       <c r="P21" s="14" t="s">
         <v>192</v>
       </c>
@@ -9675,22 +9675,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="90"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="103"/>
+    <row r="22" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="109"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="122"/>
       <c r="H22" s="86"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="120"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="102"/>
       <c r="K22" s="61"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="103"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="122"/>
       <c r="P22" s="14" t="s">
         <v>193</v>
       </c>
@@ -9704,22 +9704,22 @@
         <v>205</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103"/>
+    <row r="23" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="109"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="122"/>
       <c r="H23" s="86"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="120"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="102"/>
       <c r="K23" s="61"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="102"/>
-      <c r="N23" s="102"/>
-      <c r="O23" s="103"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="122"/>
       <c r="P23" s="14" t="s">
         <v>194</v>
       </c>
@@ -9733,22 +9733,22 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="92"/>
-      <c r="B24" s="93"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="106"/>
+    <row r="24" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="111"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="125"/>
       <c r="H24" s="87"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="121"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="103"/>
       <c r="K24" s="62"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="106"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="125"/>
       <c r="P24" s="14" t="s">
         <v>195</v>
       </c>
@@ -9762,18 +9762,18 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="149" t="s">
+    <row r="25" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="B25" s="150"/>
-      <c r="C25" s="151" t="s">
+      <c r="B25" s="145"/>
+      <c r="C25" s="146" t="s">
         <v>212</v>
       </c>
-      <c r="D25" s="151"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="146"/>
       <c r="H25" s="42" t="s">
         <v>201</v>
       </c>
@@ -9786,12 +9786,12 @@
       <c r="K25" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L25" s="111" t="s">
+      <c r="L25" s="130" t="s">
         <v>215</v>
       </c>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
+      <c r="M25" s="130"/>
+      <c r="N25" s="130"/>
+      <c r="O25" s="130"/>
       <c r="P25" s="29" t="s">
         <v>216</v>
       </c>
@@ -9805,18 +9805,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="137" t="s">
+    <row r="26" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="147" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="138"/>
-      <c r="C26" s="139" t="s">
+      <c r="B26" s="148"/>
+      <c r="C26" s="149" t="s">
         <v>217</v>
       </c>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
       <c r="H26" s="46" t="s">
         <v>201</v>
       </c>
@@ -9827,10 +9827,10 @@
         <v>219</v>
       </c>
       <c r="K26" s="48"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="141"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="142"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="151"/>
+      <c r="N26" s="151"/>
+      <c r="O26" s="152"/>
       <c r="P26" s="30" t="s">
         <v>251</v>
       </c>
@@ -9844,18 +9844,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="143" t="s">
+    <row r="27" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="153" t="s">
         <v>221</v>
       </c>
-      <c r="B27" s="144"/>
-      <c r="C27" s="145" t="s">
+      <c r="B27" s="154"/>
+      <c r="C27" s="155" t="s">
         <v>218</v>
       </c>
-      <c r="D27" s="145"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="145"/>
+      <c r="D27" s="155"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="155"/>
       <c r="H27" s="59" t="s">
         <v>49</v>
       </c>
@@ -9866,10 +9866,10 @@
         <v>220</v>
       </c>
       <c r="K27" s="51"/>
-      <c r="L27" s="146"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="148"/>
+      <c r="L27" s="156"/>
+      <c r="M27" s="157"/>
+      <c r="N27" s="157"/>
+      <c r="O27" s="158"/>
       <c r="P27" s="73" t="s">
         <v>251</v>
       </c>
@@ -9885,6 +9885,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="L21:O24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="C21:G24"/>
+    <mergeCell ref="A21:B24"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="A1:Q1"/>
@@ -9898,21 +9913,6 @@
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K19:O19"/>
     <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="L21:O24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="C21:G24"/>
-    <mergeCell ref="A21:B24"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="L27:O27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B8AB2723-0DBB-4F87-B341-FF92A393E7BB}"/>
@@ -9941,103 +9941,103 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C459138-DDE6-474C-B731-CBDFA7C0E67E}">
   <dimension ref="A1:U23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.7109375" style="8" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.42578125" style="8" customWidth="1"/>
-    <col min="21" max="21" width="25.42578125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.6640625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.44140625" style="8" customWidth="1"/>
+    <col min="21" max="21" width="25.44140625" style="8" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A9</f>
         <v>UnidadTiempoUso</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B9</f>
         <v>Objeto de dominio que representa una unidad de tiempo encargado de asignar la manera en como se va a medir el tiempo de unos de una persona según las necesidades o claridad de uso para un residente en una zona común .</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -10106,7 +10106,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>53</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>307</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>308</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>56</v>
       </c>
@@ -10339,9 +10339,13 @@
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
+      <c r="I9" s="26" t="s">
+        <v>54</v>
+      </c>
       <c r="J9" s="25"/>
-      <c r="K9" s="27"/>
+      <c r="K9" s="27" t="s">
+        <v>55</v>
+      </c>
       <c r="L9" s="25" t="s">
         <v>52</v>
       </c>
@@ -10373,15 +10377,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="159" t="s">
         <v>128</v>
       </c>
       <c r="B11" s="159"/>
       <c r="C11" s="159"/>
     </row>
-    <row r="12" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="78" t="s">
         <v>63</v>
       </c>
@@ -10392,7 +10396,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="64.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="64.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="79" t="s">
         <v>316</v>
       </c>
@@ -10403,48 +10407,48 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="135" t="s">
+    <row r="14" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118" t="s">
+      <c r="B15" s="88"/>
+      <c r="C15" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118" t="s">
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118" t="s">
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="L15" s="118"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118" t="s">
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118" t="s">
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="S15" s="125"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="136"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
+      <c r="S15" s="89"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="100"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
       <c r="H16" s="38" t="s">
         <v>70</v>
       </c>
@@ -10457,12 +10461,12 @@
       <c r="K16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="126" t="s">
+      <c r="L16" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="90"/>
       <c r="P16" s="38" t="s">
         <v>72</v>
       </c>
@@ -10476,32 +10480,32 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="88" t="s">
+    <row r="17" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="98" t="s">
+      <c r="B17" s="108"/>
+      <c r="C17" s="117" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="100"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="119"/>
       <c r="H17" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="I17" s="122" t="s">
+      <c r="I17" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="119" t="s">
+      <c r="J17" s="101" t="s">
         <v>202</v>
       </c>
       <c r="K17" s="16"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="100"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="119"/>
       <c r="P17" s="14" t="s">
         <v>192</v>
       </c>
@@ -10515,22 +10519,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103"/>
+    <row r="18" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="109"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="122"/>
       <c r="H18" s="86"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="120"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="102"/>
       <c r="K18" s="61"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="103"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="122"/>
       <c r="P18" s="14" t="s">
         <v>193</v>
       </c>
@@ -10544,22 +10548,22 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103"/>
+    <row r="19" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="109"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="86"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="120"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="102"/>
       <c r="K19" s="61"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="103"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="122"/>
       <c r="P19" s="14" t="s">
         <v>194</v>
       </c>
@@ -10573,22 +10577,22 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="92"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="106"/>
+    <row r="20" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="111"/>
+      <c r="B20" s="112"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="125"/>
       <c r="H20" s="87"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="121"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="103"/>
       <c r="K20" s="62"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="106"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="125"/>
       <c r="P20" s="14" t="s">
         <v>195</v>
       </c>
@@ -10602,18 +10606,18 @@
         <v>211</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="149" t="s">
+    <row r="21" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="150"/>
-      <c r="C21" s="151" t="s">
+      <c r="B21" s="145"/>
+      <c r="C21" s="146" t="s">
         <v>212</v>
       </c>
-      <c r="D21" s="151"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="151"/>
-      <c r="G21" s="151"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
       <c r="H21" s="42" t="s">
         <v>201</v>
       </c>
@@ -10626,12 +10630,12 @@
       <c r="K21" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L21" s="111" t="s">
+      <c r="L21" s="130" t="s">
         <v>215</v>
       </c>
-      <c r="M21" s="111"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
+      <c r="M21" s="130"/>
+      <c r="N21" s="130"/>
+      <c r="O21" s="130"/>
       <c r="P21" s="29" t="s">
         <v>216</v>
       </c>
@@ -10645,18 +10649,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="137" t="s">
+    <row r="22" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="147" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="138"/>
-      <c r="C22" s="139" t="s">
+      <c r="B22" s="148"/>
+      <c r="C22" s="149" t="s">
         <v>217</v>
       </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="139"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
       <c r="H22" s="46" t="s">
         <v>201</v>
       </c>
@@ -10667,10 +10671,10 @@
         <v>219</v>
       </c>
       <c r="K22" s="48"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="141"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="142"/>
+      <c r="L22" s="150"/>
+      <c r="M22" s="151"/>
+      <c r="N22" s="151"/>
+      <c r="O22" s="152"/>
       <c r="P22" s="30" t="s">
         <v>251</v>
       </c>
@@ -10684,18 +10688,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="143" t="s">
+    <row r="23" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="153" t="s">
         <v>221</v>
       </c>
-      <c r="B23" s="144"/>
-      <c r="C23" s="145" t="s">
+      <c r="B23" s="154"/>
+      <c r="C23" s="155" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="155"/>
+      <c r="G23" s="155"/>
       <c r="H23" s="59" t="s">
         <v>49</v>
       </c>
@@ -10706,10 +10710,10 @@
         <v>220</v>
       </c>
       <c r="K23" s="51"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="147"/>
-      <c r="O23" s="148"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="157"/>
+      <c r="O23" s="158"/>
       <c r="P23" s="73" t="s">
         <v>251</v>
       </c>
@@ -10725,13 +10729,15 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
     <mergeCell ref="L17:O20"/>
     <mergeCell ref="A15:B16"/>
     <mergeCell ref="C15:G16"/>
@@ -10742,15 +10748,13 @@
     <mergeCell ref="H17:H20"/>
     <mergeCell ref="I17:I20"/>
     <mergeCell ref="J17:J20"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{3E822B6E-3E69-4872-A72B-64DA54F35712}"/>
@@ -10778,103 +10782,103 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F029C1A4-1158-48DA-9920-018E5820E9AF}">
   <dimension ref="A1:U30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="42.85546875" style="8" customWidth="1"/>
-    <col min="19" max="19" width="36.28515625" style="8" customWidth="1"/>
-    <col min="20" max="20" width="40.85546875" style="8" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.88671875" style="8" customWidth="1"/>
+    <col min="19" max="19" width="36.33203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="40.88671875" style="8" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A5</f>
         <v>Administrador</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B5</f>
         <v>Objeto de dominio que representa el Administrador encargado de hacer la creación o gestión de las zonas comunes y la gestión de residentes y sus respectivas reservas en caso de ser necesario.</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="55" t="s">
         <v>33</v>
       </c>
@@ -10943,7 +10947,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>49</v>
       </c>
@@ -10996,7 +11000,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>53</v>
       </c>
@@ -11051,7 +11055,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>80</v>
       </c>
@@ -11106,7 +11110,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>93</v>
       </c>
@@ -11161,7 +11165,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>94</v>
       </c>
@@ -11216,7 +11220,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>108</v>
       </c>
@@ -11271,7 +11275,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>112</v>
       </c>
@@ -11324,7 +11328,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>83</v>
       </c>
@@ -11377,24 +11381,24 @@
         <v>184</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="130" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="E15" s="130" t="s">
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="E15" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="I15" s="130" t="s">
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="I15" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J15" s="94"/>
+      <c r="K15" s="94"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
         <v>63</v>
       </c>
@@ -11423,101 +11427,101 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="131" t="s">
+    <row r="17" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="131" t="s">
+      <c r="B17" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="132" t="s">
+      <c r="C17" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="131" t="s">
+      <c r="E17" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="131" t="s">
+      <c r="F17" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="132" t="s">
+      <c r="G17" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="131" t="s">
+      <c r="I17" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="131" t="s">
+      <c r="J17" s="95" t="s">
         <v>111</v>
       </c>
-      <c r="K17" s="132" t="s">
+      <c r="K17" s="96" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="131"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="132"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="132"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="132"/>
-    </row>
-    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="131"/>
-      <c r="B19" s="131"/>
+    <row r="18" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="95"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="96"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="96"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="96"/>
+    </row>
+    <row r="19" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="95"/>
+      <c r="B19" s="95"/>
       <c r="C19" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="132"/>
-      <c r="I19" s="131"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132"/>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="135" t="s">
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="96"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="96"/>
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="118" t="s">
+      <c r="B21" s="88"/>
+      <c r="C21" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118" t="s">
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118" t="s">
+      <c r="I21" s="88"/>
+      <c r="J21" s="88"/>
+      <c r="K21" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="118" t="s">
+      <c r="L21" s="88"/>
+      <c r="M21" s="88"/>
+      <c r="N21" s="88"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="Q21" s="118"/>
-      <c r="R21" s="118" t="s">
+      <c r="Q21" s="88"/>
+      <c r="R21" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="S21" s="125"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="136"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
+      <c r="S21" s="89"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="100"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
       <c r="H22" s="38" t="s">
         <v>70</v>
       </c>
@@ -11530,12 +11534,12 @@
       <c r="K22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="126" t="s">
+      <c r="L22" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
-      <c r="O22" s="126"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
       <c r="P22" s="38" t="s">
         <v>72</v>
       </c>
@@ -11549,35 +11553,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="88" t="s">
+    <row r="23" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="98" t="s">
+      <c r="B23" s="108"/>
+      <c r="C23" s="117" t="s">
         <v>242</v>
       </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="100"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="119"/>
       <c r="H23" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
       </c>
-      <c r="I23" s="122" t="str">
+      <c r="I23" s="104" t="str">
         <f>B2</f>
         <v>Administrador</v>
       </c>
-      <c r="J23" s="119" t="str">
+      <c r="J23" s="101" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Administrador</v>
       </c>
       <c r="K23" s="16"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="99"/>
-      <c r="O23" s="100"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="119"/>
       <c r="P23" s="14" t="s">
         <v>224</v>
       </c>
@@ -11591,22 +11595,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="90"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="103"/>
+    <row r="24" spans="1:19" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="109"/>
+      <c r="B24" s="110"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="122"/>
       <c r="H24" s="86"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="120"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="102"/>
       <c r="K24" s="61"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="102"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="103"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="122"/>
       <c r="P24" s="14" t="s">
         <v>225</v>
       </c>
@@ -11620,22 +11624,22 @@
         <v>234</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="90"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103"/>
+    <row r="25" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="109"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="122"/>
       <c r="H25" s="86"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="120"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="61"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="103"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="122"/>
       <c r="P25" s="14" t="s">
         <v>226</v>
       </c>
@@ -11649,22 +11653,22 @@
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="103"/>
+    <row r="26" spans="1:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="109"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="121"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="122"/>
       <c r="H26" s="86"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="120"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="102"/>
       <c r="K26" s="61"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="103"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="122"/>
       <c r="P26" s="14" t="s">
         <v>227</v>
       </c>
@@ -11678,22 +11682,22 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="106"/>
+    <row r="27" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="111"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="125"/>
       <c r="H27" s="87"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="121"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="103"/>
       <c r="K27" s="62"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="105"/>
-      <c r="O27" s="106"/>
+      <c r="L27" s="123"/>
+      <c r="M27" s="124"/>
+      <c r="N27" s="124"/>
+      <c r="O27" s="125"/>
       <c r="P27" s="14" t="s">
         <v>228</v>
       </c>
@@ -11707,18 +11711,18 @@
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="149" t="s">
+    <row r="28" spans="1:19" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="B28" s="150"/>
-      <c r="C28" s="151" t="s">
+      <c r="B28" s="145"/>
+      <c r="C28" s="146" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="146"/>
       <c r="H28" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -11734,12 +11738,12 @@
       <c r="K28" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L28" s="111" t="s">
+      <c r="L28" s="130" t="s">
         <v>245</v>
       </c>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="130"/>
+      <c r="O28" s="130"/>
       <c r="P28" s="29" t="s">
         <v>240</v>
       </c>
@@ -11753,18 +11757,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="88.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="137" t="s">
+    <row r="29" spans="1:19" ht="88.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="147" t="s">
         <v>153</v>
       </c>
-      <c r="B29" s="138"/>
-      <c r="C29" s="139" t="s">
+      <c r="B29" s="148"/>
+      <c r="C29" s="149" t="s">
         <v>243</v>
       </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="149"/>
+      <c r="G29" s="149"/>
       <c r="H29" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosAdministrador</v>
@@ -11778,10 +11782,10 @@
         <v>Corresponde a los datos que se van a modificar de la Administrador</v>
       </c>
       <c r="K29" s="48"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="142"/>
+      <c r="L29" s="150"/>
+      <c r="M29" s="151"/>
+      <c r="N29" s="151"/>
+      <c r="O29" s="152"/>
       <c r="P29" s="30" t="s">
         <v>250</v>
       </c>
@@ -11795,18 +11799,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="143" t="s">
+    <row r="30" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="153" t="s">
         <v>221</v>
       </c>
-      <c r="B30" s="144"/>
-      <c r="C30" s="145" t="s">
+      <c r="B30" s="154"/>
+      <c r="C30" s="155" t="s">
         <v>244</v>
       </c>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="155"/>
+      <c r="F30" s="155"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="59" t="s">
         <v>49</v>
       </c>
@@ -11818,10 +11822,10 @@
         <v>Corresponde al identificador del Administrador  que se quiere dar de baja.</v>
       </c>
       <c r="K30" s="51"/>
-      <c r="L30" s="146"/>
-      <c r="M30" s="147"/>
-      <c r="N30" s="147"/>
-      <c r="O30" s="148"/>
+      <c r="L30" s="156"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="158"/>
       <c r="P30" s="73" t="s">
         <v>250</v>
       </c>
@@ -11837,6 +11841,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="L23:O27"/>
+    <mergeCell ref="A23:B27"/>
+    <mergeCell ref="C23:G27"/>
+    <mergeCell ref="H23:H27"/>
+    <mergeCell ref="I23:I27"/>
+    <mergeCell ref="J23:J27"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:O21"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="L22:O22"/>
     <mergeCell ref="A1:Q1"/>
@@ -11853,27 +11878,6 @@
     <mergeCell ref="J17:J19"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="G17:G19"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K21:O21"/>
-    <mergeCell ref="K17:K19"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="L23:O27"/>
-    <mergeCell ref="A23:B27"/>
-    <mergeCell ref="C23:G27"/>
-    <mergeCell ref="H23:H27"/>
-    <mergeCell ref="I23:I27"/>
-    <mergeCell ref="J23:J27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{B1A972F6-B36A-42D4-994E-AD97A6BC793F}"/>
@@ -11906,103 +11910,103 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7CF9007-2408-46A6-B9E2-87DBBD723E5F}">
   <dimension ref="A1:U24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A6</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B6</f>
         <v>Objeto de dominio que representa una zona de inmuebles en un conjunto residencial se refiere a una agrupación de unidades habitacionales (torre, bloque, lote) que comparten una ubicación fisica y caracteristicas comunes dentro del conjunto.</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -12070,7 +12074,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -12123,7 +12127,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>86</v>
       </c>
@@ -12182,7 +12186,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>85</v>
       </c>
@@ -12219,7 +12223,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>60</v>
       </c>
@@ -12266,15 +12270,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="152" t="s">
+    <row r="9" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="153"/>
-      <c r="C10" s="154"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="138"/>
+      <c r="C10" s="139"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>63</v>
       </c>
@@ -12285,73 +12289,73 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="177" t="s">
+    <row r="12" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="183" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="142" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="70" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="178"/>
-      <c r="B13" s="180"/>
+    <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="184"/>
+      <c r="B13" s="186"/>
       <c r="C13" s="36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="179"/>
-      <c r="B14" s="158"/>
+    <row r="14" spans="1:21" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="185"/>
+      <c r="B14" s="143"/>
       <c r="C14" s="37" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="181" t="s">
+    <row r="15" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="182"/>
-      <c r="C16" s="185" t="s">
+      <c r="B16" s="188"/>
+      <c r="C16" s="191" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="172" t="s">
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="192"/>
+      <c r="G16" s="188"/>
+      <c r="H16" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="189"/>
-      <c r="J16" s="190"/>
-      <c r="K16" s="172" t="s">
+      <c r="I16" s="195"/>
+      <c r="J16" s="196"/>
+      <c r="K16" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="189"/>
-      <c r="M16" s="189"/>
-      <c r="N16" s="189"/>
-      <c r="O16" s="190"/>
-      <c r="P16" s="172" t="s">
+      <c r="L16" s="195"/>
+      <c r="M16" s="195"/>
+      <c r="N16" s="195"/>
+      <c r="O16" s="196"/>
+      <c r="P16" s="178" t="s">
         <v>68</v>
       </c>
-      <c r="Q16" s="190"/>
-      <c r="R16" s="172" t="s">
+      <c r="Q16" s="196"/>
+      <c r="R16" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="S16" s="173"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="183"/>
-      <c r="B17" s="184"/>
-      <c r="C17" s="187"/>
-      <c r="D17" s="188"/>
-      <c r="E17" s="188"/>
-      <c r="F17" s="188"/>
-      <c r="G17" s="184"/>
+      <c r="S16" s="179"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="189"/>
+      <c r="B17" s="190"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="190"/>
       <c r="H17" s="38" t="s">
         <v>70</v>
       </c>
@@ -12364,12 +12368,12 @@
       <c r="K17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="174" t="s">
+      <c r="L17" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="175"/>
-      <c r="N17" s="175"/>
-      <c r="O17" s="176"/>
+      <c r="M17" s="181"/>
+      <c r="N17" s="181"/>
+      <c r="O17" s="182"/>
       <c r="P17" s="38" t="s">
         <v>72</v>
       </c>
@@ -12383,35 +12387,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="160" t="s">
+    <row r="18" spans="1:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="197" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="161"/>
-      <c r="C18" s="164" t="s">
+      <c r="B18" s="198"/>
+      <c r="C18" s="201" t="s">
         <v>247</v>
       </c>
-      <c r="D18" s="165"/>
-      <c r="E18" s="165"/>
-      <c r="F18" s="165"/>
-      <c r="G18" s="166"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="202"/>
+      <c r="G18" s="203"/>
       <c r="H18" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
       </c>
-      <c r="I18" s="170" t="str">
+      <c r="I18" s="207" t="str">
         <f>B2</f>
         <v>ZonaInmueble</v>
       </c>
-      <c r="J18" s="119" t="str">
+      <c r="J18" s="101" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ZonaInmueble</v>
       </c>
       <c r="K18" s="16"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="100"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="119"/>
       <c r="P18" s="14" t="s">
         <v>252</v>
       </c>
@@ -12425,22 +12429,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="162"/>
-      <c r="B19" s="163"/>
-      <c r="C19" s="167"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="169"/>
+    <row r="19" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="199"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="204"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="205"/>
+      <c r="G19" s="206"/>
       <c r="H19" s="86"/>
-      <c r="I19" s="171"/>
-      <c r="J19" s="120"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="102"/>
       <c r="K19" s="61"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="103"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="122"/>
       <c r="P19" s="14" t="s">
         <v>254</v>
       </c>
@@ -12454,22 +12458,22 @@
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="162"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="167"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="169"/>
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="199"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="204"/>
+      <c r="D20" s="205"/>
+      <c r="E20" s="205"/>
+      <c r="F20" s="205"/>
+      <c r="G20" s="206"/>
       <c r="H20" s="86"/>
-      <c r="I20" s="171"/>
-      <c r="J20" s="120"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="102"/>
       <c r="K20" s="61"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="102"/>
-      <c r="N20" s="102"/>
-      <c r="O20" s="103"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="122"/>
       <c r="P20" s="14" t="s">
         <v>255</v>
       </c>
@@ -12483,22 +12487,22 @@
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="162"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="167"/>
-      <c r="D21" s="168"/>
-      <c r="E21" s="168"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="169"/>
+    <row r="21" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="199"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="204"/>
+      <c r="D21" s="205"/>
+      <c r="E21" s="205"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="206"/>
       <c r="H21" s="86"/>
-      <c r="I21" s="171"/>
-      <c r="J21" s="120"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="102"/>
       <c r="K21" s="61"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="122"/>
       <c r="P21" s="14" t="s">
         <v>256</v>
       </c>
@@ -12512,18 +12516,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="196" t="s">
+    <row r="22" spans="1:19" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="165" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="197"/>
-      <c r="C22" s="198" t="s">
+      <c r="B22" s="166"/>
+      <c r="C22" s="167" t="s">
         <v>246</v>
       </c>
-      <c r="D22" s="199"/>
-      <c r="E22" s="199"/>
-      <c r="F22" s="199"/>
-      <c r="G22" s="200"/>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="169"/>
       <c r="H22" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
@@ -12539,12 +12543,12 @@
       <c r="K22" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L22" s="201" t="s">
+      <c r="L22" s="170" t="s">
         <v>215</v>
       </c>
-      <c r="M22" s="202"/>
-      <c r="N22" s="202"/>
-      <c r="O22" s="203"/>
+      <c r="M22" s="171"/>
+      <c r="N22" s="171"/>
+      <c r="O22" s="172"/>
       <c r="P22" s="29" t="s">
         <v>262</v>
       </c>
@@ -12558,18 +12562,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="204" t="s">
+    <row r="23" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="173" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="205"/>
-      <c r="C23" s="206" t="s">
+      <c r="B23" s="174"/>
+      <c r="C23" s="175" t="s">
         <v>248</v>
       </c>
-      <c r="D23" s="207"/>
-      <c r="E23" s="207"/>
-      <c r="F23" s="207"/>
-      <c r="G23" s="208"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="177"/>
       <c r="H23" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosZonaInmueble</v>
@@ -12583,10 +12587,10 @@
         <v>Corresponde a los datos que se van a modificar de la ZonaInmueble</v>
       </c>
       <c r="K23" s="48"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="141"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="142"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="151"/>
+      <c r="N23" s="151"/>
+      <c r="O23" s="152"/>
       <c r="P23" s="69" t="s">
         <v>263</v>
       </c>
@@ -12600,18 +12604,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="191" t="s">
+    <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="160" t="s">
         <v>221</v>
       </c>
-      <c r="B24" s="192"/>
-      <c r="C24" s="193" t="s">
+      <c r="B24" s="161"/>
+      <c r="C24" s="162" t="s">
         <v>249</v>
       </c>
-      <c r="D24" s="194"/>
-      <c r="E24" s="194"/>
-      <c r="F24" s="194"/>
-      <c r="G24" s="195"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="163"/>
+      <c r="G24" s="164"/>
       <c r="H24" s="59" t="s">
         <v>49</v>
       </c>
@@ -12623,10 +12627,10 @@
         <v>Corresponde al identificador de la ZonaInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K24" s="51"/>
-      <c r="L24" s="146"/>
-      <c r="M24" s="147"/>
-      <c r="N24" s="147"/>
-      <c r="O24" s="148"/>
+      <c r="L24" s="156"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="158"/>
       <c r="P24" s="31" t="s">
         <v>263</v>
       </c>
@@ -12642,15 +12646,12 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="L18:O21"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="C18:G21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="A1:Q1"/>
@@ -12664,12 +12665,15 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="K16:O16"/>
     <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="L18:O21"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C18:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="L23:O23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{00F0F8F7-DC0F-4454-B174-288E79B7BE78}"/>
@@ -12699,103 +12703,103 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A7D931-9398-4286-A42F-F0B08EACCC83}">
   <dimension ref="A1:U20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="8"/>
+    <col min="17" max="17" width="94.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="128" t="str">
+      <c r="B2" s="92" t="str">
         <f>'Listado Objetos Dominio'!A8</f>
         <v>TipoZonaInmueble</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="129" t="str">
+      <c r="B3" s="93" t="str">
         <f>'Listado Objetos Dominio'!B8</f>
         <v>Objeto de dominio que representa un tipo de zona inmueble encargado de hacer la creación de nuevas zonas inmuebles para el conjunto residencial como torres, bloques , manzanas etc .</v>
       </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>33</v>
       </c>
@@ -12863,7 +12867,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -12916,7 +12920,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>53</v>
       </c>
@@ -12969,15 +12973,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="159" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="159"/>
       <c r="C8" s="159"/>
     </row>
-    <row r="9" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="78" t="s">
         <v>63</v>
       </c>
@@ -12988,7 +12992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="55.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="56.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="79" t="s">
         <v>322</v>
       </c>
@@ -13000,48 +13004,48 @@
         <v>nombre</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="181" t="s">
+    <row r="11" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="182"/>
-      <c r="C12" s="185" t="s">
+      <c r="B12" s="188"/>
+      <c r="C12" s="191" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="182"/>
-      <c r="H12" s="172" t="s">
+      <c r="D12" s="192"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="188"/>
+      <c r="H12" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="189"/>
-      <c r="J12" s="190"/>
-      <c r="K12" s="172" t="s">
+      <c r="I12" s="195"/>
+      <c r="J12" s="196"/>
+      <c r="K12" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="L12" s="189"/>
-      <c r="M12" s="189"/>
-      <c r="N12" s="189"/>
-      <c r="O12" s="190"/>
-      <c r="P12" s="172" t="s">
+      <c r="L12" s="195"/>
+      <c r="M12" s="195"/>
+      <c r="N12" s="195"/>
+      <c r="O12" s="196"/>
+      <c r="P12" s="178" t="s">
         <v>68</v>
       </c>
-      <c r="Q12" s="190"/>
-      <c r="R12" s="172" t="s">
+      <c r="Q12" s="196"/>
+      <c r="R12" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="S12" s="173"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="183"/>
-      <c r="B13" s="184"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="188"/>
-      <c r="G13" s="184"/>
+      <c r="S12" s="179"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="189"/>
+      <c r="B13" s="190"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
+      <c r="F13" s="194"/>
+      <c r="G13" s="190"/>
       <c r="H13" s="38" t="s">
         <v>70</v>
       </c>
@@ -13054,12 +13058,12 @@
       <c r="K13" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="174" t="s">
+      <c r="L13" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="175"/>
-      <c r="N13" s="175"/>
-      <c r="O13" s="176"/>
+      <c r="M13" s="181"/>
+      <c r="N13" s="181"/>
+      <c r="O13" s="182"/>
       <c r="P13" s="38" t="s">
         <v>72</v>
       </c>
@@ -13073,35 +13077,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="160" t="s">
+    <row r="14" spans="1:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="197" t="s">
         <v>151</v>
       </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="164" t="s">
+      <c r="B14" s="198"/>
+      <c r="C14" s="201" t="s">
         <v>247</v>
       </c>
-      <c r="D14" s="165"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="165"/>
-      <c r="G14" s="166"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="202"/>
+      <c r="G14" s="203"/>
       <c r="H14" s="85" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
       </c>
-      <c r="I14" s="170" t="str">
+      <c r="I14" s="207" t="str">
         <f>B2</f>
         <v>TipoZonaInmueble</v>
       </c>
-      <c r="J14" s="119" t="str">
+      <c r="J14" s="101" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva TipoZonaInmueble</v>
       </c>
       <c r="K14" s="16"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
-      <c r="O14" s="100"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="119"/>
       <c r="P14" s="14" t="s">
         <v>252</v>
       </c>
@@ -13115,22 +13119,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="162"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="169"/>
+    <row r="15" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="199"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="205"/>
+      <c r="G15" s="206"/>
       <c r="H15" s="86"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="120"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="102"/>
       <c r="K15" s="61"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="103"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="122"/>
       <c r="P15" s="14" t="s">
         <v>254</v>
       </c>
@@ -13144,22 +13148,22 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="169"/>
+    <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="199"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="205"/>
+      <c r="F16" s="205"/>
+      <c r="G16" s="206"/>
       <c r="H16" s="86"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="120"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="102"/>
       <c r="K16" s="61"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="103"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="122"/>
       <c r="P16" s="14" t="s">
         <v>255</v>
       </c>
@@ -13173,22 +13177,22 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="162"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="169"/>
+    <row r="17" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="199"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="205"/>
+      <c r="E17" s="205"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="206"/>
       <c r="H17" s="86"/>
-      <c r="I17" s="171"/>
-      <c r="J17" s="120"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="102"/>
       <c r="K17" s="61"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="103"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="122"/>
       <c r="P17" s="14" t="s">
         <v>256</v>
       </c>
@@ -13202,18 +13206,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="61.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="196" t="s">
+    <row r="18" spans="1:19" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="165" t="s">
         <v>152</v>
       </c>
-      <c r="B18" s="197"/>
-      <c r="C18" s="198" t="s">
+      <c r="B18" s="166"/>
+      <c r="C18" s="167" t="s">
         <v>246</v>
       </c>
-      <c r="D18" s="199"/>
-      <c r="E18" s="199"/>
-      <c r="F18" s="199"/>
-      <c r="G18" s="200"/>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="169"/>
       <c r="H18" s="42" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
@@ -13229,12 +13233,12 @@
       <c r="K18" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="L18" s="201" t="s">
+      <c r="L18" s="170" t="s">
         <v>215</v>
       </c>
-      <c r="M18" s="202"/>
-      <c r="N18" s="202"/>
-      <c r="O18" s="203"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="172"/>
       <c r="P18" s="29" t="s">
         <v>262</v>
       </c>
@@ -13248,18 +13252,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="204" t="s">
+    <row r="19" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="173" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="205"/>
-      <c r="C19" s="206" t="s">
+      <c r="B19" s="174"/>
+      <c r="C19" s="175" t="s">
         <v>248</v>
       </c>
-      <c r="D19" s="207"/>
-      <c r="E19" s="207"/>
-      <c r="F19" s="207"/>
-      <c r="G19" s="208"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="177"/>
       <c r="H19" s="46" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosTipoZonaInmueble</v>
@@ -13273,10 +13277,10 @@
         <v>Corresponde a los datos que se van a modificar de la TipoZonaInmueble</v>
       </c>
       <c r="K19" s="48"/>
-      <c r="L19" s="140"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="142"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="151"/>
+      <c r="N19" s="151"/>
+      <c r="O19" s="152"/>
       <c r="P19" s="69" t="s">
         <v>263</v>
       </c>
@@ -13290,18 +13294,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="191" t="s">
+    <row r="20" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="160" t="s">
         <v>221</v>
       </c>
-      <c r="B20" s="192"/>
-      <c r="C20" s="193" t="s">
+      <c r="B20" s="161"/>
+      <c r="C20" s="162" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="194"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="194"/>
-      <c r="G20" s="195"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163"/>
+      <c r="F20" s="163"/>
+      <c r="G20" s="164"/>
       <c r="H20" s="59" t="s">
         <v>49</v>
       </c>
@@ -13313,10 +13317,10 @@
         <v>Corresponde al identificador de la TipoZonaInmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K20" s="51"/>
-      <c r="L20" s="146"/>
-      <c r="M20" s="147"/>
-      <c r="N20" s="147"/>
-      <c r="O20" s="148"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="157"/>
+      <c r="O20" s="158"/>
       <c r="P20" s="31" t="s">
         <v>263</v>
       </c>
@@ -13332,13 +13336,15 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="L19:O19"/>
     <mergeCell ref="L14:O17"/>
     <mergeCell ref="A12:B13"/>
     <mergeCell ref="C12:G13"/>
@@ -13349,15 +13355,13 @@
     <mergeCell ref="H14:H17"/>
     <mergeCell ref="I14:I17"/>
     <mergeCell ref="J14:J17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{ADA2A2A6-5B57-4F87-8E96-63F5687CC6C2}"/>
